--- a/assets/FAIRe_checklist_v1.0.2.xlsx
+++ b/assets/FAIRe_checklist_v1.0.2.xlsx
@@ -33,12 +33,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A list (concatenated and separated) of names of people responsible for the submitted dataset
 Example : José E. Crespo
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -50,12 +49,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A contact person and their contact (i.e., email address) for data enquiry
 Example : xxxx@yyyy.com
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -67,12 +65,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A brief, concise project identifier with no spaces or special characters, ensuring machine readability. This ID will be used in data file names as 'project_id'.
 Example : noaa-aoml-gomecc4
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -84,12 +81,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : The method used in the eDNA study to detect taxon/taxa of interest in environmental sample. A targeted eDNA assay is designed to detect the presence of a specific species or a small subset of taxa (such as a genus or family) using techniques like quantitative PCR (qPCR). This contrasts with a metabarcoding eDNA assay which aims to characterize the composition of broader taxonomic communities, often encompassing multiple phyletic groups, by utilising high-throughput sequencing such as metabarcoding
 Example : targeted
-Field type : controlled vocabulary (targeted | metabarcoding | other:)
-</t>
+Field type : controlled vocabulary (targeted | metabarcoding | other:)</t>
         </r>
       </text>
     </comment>
@@ -101,12 +97,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : the protocols to minimise contaminations in the field and/or laboratory
 Example : Sampling bottles were rinsed with 10% bleached and DI water. Single-use syringes and capsule filters were used for filtration. Single-use gloves were used to collect and filter each sample.
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -118,12 +113,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Were negative controls applied during the project? Yes = 1, No = 0. For further details, record the types of negative controls under the term neg_cont_type in sampleMetadata
 Example : 1
-Field type : Boolean
-</t>
+Field type : Boolean</t>
         </r>
       </text>
     </comment>
@@ -135,12 +129,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Were positive controls applied during the project? Yes = 1, No = 0. For further details, record the types of positive controls under the term pos_cont_type in sampleMetadata
 Example : 1
-Field type : Boolean
-</t>
+Field type : Boolean</t>
         </r>
       </text>
     </comment>
@@ -152,12 +145,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : The version number of the FAIR eDNA (FAIRe) metadata checklist used to format the data
 Example : 1.2
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -169,12 +161,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : Was PCR performed in the study? Yes = 1, No (pcr-free approaches including shotgun metagenomics, Nanopore) = 0
 Example : 1
-Field type : Boolean
-</t>
+Field type : Boolean</t>
         </r>
       </text>
     </comment>
@@ -186,12 +177,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A brief, concise identifier for assay with no spaces or special characters, ensuring machine readability. This ID will be used in file names as 'assay_name'.
 Example : MiFish (metabarcoding) / eSERU5 (qPCR)
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -203,12 +193,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If pcr_0_1 is 1. Else, recommended)
 Description : Taxa or species name targeted by the primers, probes, and/or other approaches applied in the PCR.
 Example : verteberate
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -220,12 +209,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Targeted gene or locus name for marker gene studies
 Example : COI
-Field type : controlled vocabulary (12S rRNA (SSU mitochondria) | 16S rRNA (LSU mitochondria) | 16S rRNA (SSU prokaryote) | 23S rRNA (LSU prokaryote) | 18S rRNA (SSU eukaryote) | 28S rRNA (LSU eukaryote) | rbcL | CytB | COI | COII | COIII | nifH | ITS | ND1 | ND2 | ND3 | ND4 | ND5 | ND6 | amoA | rpoB | rpoC1 | rpoC2 | matK | trnH | trnL | psbK | D-loop | other:)
-</t>
+Field type : controlled vocabulary (12S rRNA (SSU mitochondria) | 16S rRNA (LSU mitochondria) | 16S rRNA (SSU prokaryote) | 23S rRNA (LSU prokaryote) | 18S rRNA (SSU eukaryote) | 28S rRNA (LSU eukaryote) | rbcL | CytB | COI | COII | COIII | nifH | ITS | ND1 | ND2 | ND3 | ND4 | ND5 | ND6 | amoA | rpoB | rpoC1 | rpoC2 | matK | trnH | trnL | psbK | D-loop | other:)</t>
         </r>
       </text>
     </comment>
@@ -237,12 +225,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The length of the amplicon in basepairs EXCLUDING the primers, adapters and MIDs. A range can be entered separated by a hyphen"-" (i.e. 140-160). If using Excel, format the cell as text to prevent it from being auto-formatted as a date. Unit = basepairs
 Example : 83
-Field type : integer
-</t>
+Field type : integer</t>
         </r>
       </text>
     </comment>
@@ -254,12 +241,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If pcr_0_1 is 1)
 Description : Forward PCR primer (5' - 3') that were used to amplify the sequence of the targeted gene. The primer sequence should NOT contain MIDs and adapter sequences, and should be reported in uppercase letters. If multiple forward primers are present in a single PCR reaction, either report them separately in separate submissions (with separate OTU tables for each primer set), or list the primers here separated by pipe ( | ) and provide one OTU table resulting from all the primers applied here. The latter is recommended only when the multiple primers target the same gene region and thus a single OTU table was generated from the multiplexed PCR. This term is required except for PCR free methods.
 Example : GGWACWGGWTGAACWGTWTAYCCYCC
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -271,12 +257,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If pcr_0_1 is 1)
 Description : Reverse PCR primer (5' - 3') that were used to amplify the sequence of the targeted gene. The primer sequence should NOT contain MIDs and adapter sequences, and should be reported in uppercase letters. If multiple reverse primers are present in a single PCR reaction, either report them separately in separate submissions (with separate OTU tables for each primer set), or list the primers here separated by pipe ( | ) and provide one OTU table resulting from all the primers applied here. The latter is recommended only when the multiple primers target the same gene region and thus a single OTU table was generated from the multiplexed PCR. This term is required except for PCR free methods.
 Example : GGRGGRTASACSGTTCASCCSGTSCC
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -288,12 +273,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Reference (i.e. DOI) of the pcr_primer_forward. If multiple primers are listed in pcr_primer_forward, list the references respectively, separated by pipe ( | ).
 Example : https://doi.org/10.1186/1742-9994-10-34
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -305,12 +289,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Reference (i.e. DOI) of the pcr_primer_reverse. If multiple primers are listed in pcr_primer_reverse, list the references respectively, separated by pipe ( | ).
 Example : https://doi.org/10.1186/1742-9994-10-34
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -322,12 +305,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Type of fluorophore (reporter) used. Probe anneals within amplified target DNA. Polymerase activity degrades the probe that has annealed to the template, and the probe releases the fluorophore from it and breaks the proximity to the quencher, thus allowing fluorescence of the fluorophore.
 Example : FAM
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -339,12 +321,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Type of quencher used. The quencher molecule quenches the fluorescence emitted by the fluorophore when excited by the cycler’s light source As long as fluorophore and the quencher are in proximity, quenching inhibits any fluorescence signals.
 Example : MGB
-Field type : controlled vocabulary (Zero-End Quencher (ZEN) | TAMRA | lowa Black | Minor Groove Binder (MGB) | Black Hole Quencher (BHQ) | other:)
-</t>
+Field type : controlled vocabulary (Zero-End Quencher (ZEN) | TAMRA | lowa Black | Minor Groove Binder (MGB) | Black Hole Quencher (BHQ) | other:)</t>
         </r>
       </text>
     </comment>
@@ -356,12 +337,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : If applicable, probe sequence in the 5' to 3' direction
 Example : CTTGTTTGTTTGATCAATTC
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -373,12 +353,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Reference (i.e. DOI) of the probe_seq
 Example : 10.1007/s00227-017-3141-x
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -390,12 +369,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The stock concentration of the probe if applicable. This refers specifically to the concentration of the probe stock solution, not the final concentration in the PCR reaction. For example, using 1 µL of a 5 µM (stock concentration) probe in a 25 µL reaction results in a final concentration of 0.2 µM. Hence the entry for this term would be 5. Unit = µM
 Example : 100.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -407,12 +385,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Name, brand, and manufacture of commercial, pre-made master mix (if commercial master mix was used)
 Example : Luna® Universal qPCR Master Mix, New England Biolabs
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -424,12 +401,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : composition of custom master mix, including the names, volumes and concentrations of additives (i.e., salts, buffers, enzyme and other components) (if custom master mix was used)
 Example : Each PCR reaction comprised: 1 x Taq Gold buffer (Applied Biosystems [ABI], USA), 2 nM MgCl2 (ABI, USA), 0.4 mg/mL BSA (Fisher Biotec, Australia), 0.25 mM dNTPs (Astral Scientific, Australia), 0.4 μM each of forward and reverse primers (Integrated DNA Technologies, Australia), 0.6 μL of 1/10,000 SYBR Green dye (Life Technologies, USA), 1 U of Taq polymerase Gold (ABI, USA), 2 μL of DNA, and made up to 25 μL with PCR grade water
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -441,12 +417,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Volume of DNA added in each PCR reaction. Unit = µL
 Example : 2.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -458,12 +433,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The number of PCR technical replicates. For metabarcoding, each replicate should employ an identical MID.
 Example : 3
-Field type : integer
-</t>
+Field type : integer</t>
         </r>
       </text>
     </comment>
@@ -475,12 +449,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Description of reaction conditions and components of PCR. The recommended format is ´initial denaturation:degrees_minutes;annealing:degrees_minutes;elongation:degrees_minutes;final elongation:degrees_minutes;total cycles´, where possible. If two-step PCR was applied for a metabarcoding approach, enter the second PCR protocol under the term pcr2_cond in the library preparation/sequencing section.
 Example : initial denaturation:94_3;annealing:50_1;elongation:72_1.5;final elongation:72_10;35
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -492,12 +465,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The reaction temperature during the annealing phase of PCR. If two-step PCR was applied for a metabarcoding approach, enter the second PCR protocol under the term pcr2_* in the library preparation/sequencing section. Unit = degree Celsius
 Example : 60.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -509,12 +481,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Number of PCR cycles. If two-step PCR was applied for a metabarcoding approach, enter the second PCR protocol under the term pcr2_* in the library preparation/sequencing section. Unit = cycles
 Example : 40
-Field type : integer
-</t>
+Field type : integer</t>
         </r>
       </text>
     </comment>
@@ -526,12 +497,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; pcr_0_1 = 1)
 Description : Amplicon visualisation method (i.e., qPCR, dPCR, gel electrophoresis, PCR capillary electrophoresis (PCR-CE), Loop-mediated isothermal amplification (LAMP)) to determine the detection of a targeted taxon
 Example : qPCR
-Field type : controlled vocabulary (qPCR | dPCR | gel electrophoresis | CE-PCR | LAMP | other:)
-</t>
+Field type : controlled vocabulary (qPCR | dPCR | gel electrophoresis | CE-PCR | LAMP | other:)</t>
         </r>
       </text>
     </comment>
@@ -543,12 +513,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; pcr_0_1 = 1)
 Description : Criteria to determine positive detection. For example, a certain number of positive amplifications per sample, sanger sequencing of amplicons
 Example : The minimum number of PCR replicates of 2 with positive amplification
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -560,12 +529,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; pcr_0_1 = 1)
 Description : Assay's limit of detection (LOD) (the lowest amount of target taxon DNA that can be detected with a defined level of confidence).
 Example : 51.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -577,12 +545,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; pcr_0_1 = 1)
 Description : Unit for pcr_assay_lod
 Example : ng/µL
-Field type : controlled vocabulary (copies/reaction | copies/µL | ng/reaction | ng/µL | other:)
-</t>
+Field type : controlled vocabulary (copies/reaction | copies/µL | ng/reaction | ng/µL | other:)</t>
         </r>
       </text>
     </comment>
@@ -594,12 +561,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; pcr_0_1 = 1)
 Description : Assay's limit of quantification (LOQ) (the lowest amount of target taxon DNA that can be quantitatively determined with a stated precision under the stated experimental conditions).
 Example : 184.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -611,12 +577,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; pcr_0_1 = 1)
 Description : unit for pcr_assay_loq
 Example : ng/µL
-Field type : controlled vocabulary (copies/reaction | copies/µL | ng/reaction | ng/µL | other:)
-</t>
+Field type : controlled vocabulary (copies/reaction | copies/µL | ng/reaction | ng/µL | other:)</t>
         </r>
       </text>
     </comment>
@@ -628,12 +593,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; amp_vis_method = qPCR)
 Description : Threshold for change in fluorescence signal between cycles. No unit.
 Example : 0.3
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -645,12 +609,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : PCR approach for metabarcoding
 Example : two-step PCR
-Field type : controlled vocabulary (one-step PCR | two-step PCR | ligation-based | other:)
-</t>
+Field type : controlled vocabulary (one-step PCR | two-step PCR | ligation-based | other:)</t>
         </r>
       </text>
     </comment>
@@ -662,12 +625,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : General sequencing platform used.
 Example : ILLUMINA
-Field type : controlled vocabulary (ILLUMINA | BGISEQ | CAPILLARY | DNBSEQ | ELEMENT | GENAPSYS | GENEMIND | HELICOS | ION_TORRENT | LS454 | OXFORD_NANOPORE | PACBIO_SMRT | TAPESTRI | VELA_DIAGNOSTICS | ULTIMA | other:)
-</t>
+Field type : controlled vocabulary (ILLUMINA | BGISEQ | CAPILLARY | DNBSEQ | ELEMENT | GENAPSYS | GENEMIND | HELICOS | ION_TORRENT | LS454 | OXFORD_NANOPORE | PACBIO_SMRT | TAPESTRI | VELA_DIAGNOSTICS | ULTIMA | other:)</t>
         </r>
       </text>
     </comment>
@@ -679,12 +641,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Sequencing instrument (manufacturer and model) used. Where possible the term should be taken from the OBI list of DNA sequencers (https://ontobee.org/ontology/OBI?iri=http://purl.obolibrary.org/obo/OBI_0002750)
 Example : Illumina HiSeq 1500 [OBI_0003386]
-Field type : fixed format (NA)
-</t>
+Field type : fixed format (NA)</t>
         </r>
       </text>
     </comment>
@@ -696,12 +657,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The name of sequencing kit
 Example : NextSeq 500/550 v2.5
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -713,12 +673,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Specific enrichment or screening methods applied before and/or after creating libraries
 Example : The library was size selected using a Pippin-Prep (Sage Science, Beverly, USA), purified using the Qiaquick PCR Purification Kit (Qiagen), quantified using a Qubit (Invitrogen) and diluted to 2 nM before loading it onto a MiSeq Flow Cell
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -730,12 +689,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : List of reference database(s) (i.e. sequences not generated as part of the current study) along with version number, that were used to assign taxonomy to OTUs or ASVs. If custom database was used, enter 'custom' here, and provide the information of the database under the term otu_db_custom
 Example : NCBI GenBank Release 260.0 | custom
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -747,12 +705,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : High-level category of taxonomic assignment approach. Examples using sequence similarity: BLAST/MegaBLAST, USEARCH/VSEARCH. Examples using sequence composition: naive Bayes classifier, CLARK, Kraken. Examples using phylogeny: SEPP, EPA-ng, pplacer. Examples using probabilistic: PROTAX, TIPP.
 Example : sequence similarity
-Field type : controlled vocabulary (sequence similarity | sequence composition | phylogeny | probabilistic | other:)
-</t>
+Field type : controlled vocabulary (sequence similarity | sequence composition | phylogeny | probabilistic | other:)</t>
         </r>
       </text>
     </comment>
@@ -764,12 +721,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Alignment tool/software used for taxonomic assignment
 Example : blastn;2.6.0+
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -781,12 +737,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended (if screen_contam_0_1 is 1)
 Description : How were contaminations screened and applied in data curation/analyses/interpretation?
 Example : Taxa detected in negative controls were checked, and the read counts were applied as a cutoff to call presence.
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -809,12 +764,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A type/category of a sample. 'Sample" includes biological and technical replicates. If negative or positive control was selected, provide further information under the terms fill neg_cont_type and pos_cont_type.
 Example : sample
-Field type : controlled vocabulary (sample | negative control | positive control | PCR standard | other:)
-</t>
+Field type : controlled vocabulary (sample | negative control | positive control | PCR standard | other:)</t>
         </r>
       </text>
     </comment>
@@ -826,12 +780,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If samp_category = negative control)
 Description : A negative control type used in an investigation. See Table 2 in Klymus et al. 2024 (DOI: 10.3897/mbmg.8.128689) for the description of each control type, how and why it's created. For example, process negative is a sample added during processing that lacks target DNA, such as blank filter papers.
 Example : field negative | process negative | extraction negative | PCR negative
-Field type : controlled vocabulary (site negative | field negative | process negative | extraction negative | PCR negative | other:)
-</t>
+Field type : controlled vocabulary (site negative | field negative | process negative | extraction negative | PCR negative | other:)</t>
         </r>
       </text>
     </comment>
@@ -843,12 +796,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If samp_category = positive control)
 Description : A positive control type used in an investigation. See Table 2 in Klymus et al. 2024 (DOI: 10.3897/mbmg.8.128689) for the description of each control type, how and why it's created. For example, PCR positive is a introduced target material to monitor for PCR success, including moch community samples. Provide further details (e.g., synthetic DNA) where applicable.
 Example : PCR positive of synthetic DNA
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -860,12 +812,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">tak025:
+          <t>tak025:
 Requirement level : Optional
 Description : This term refers to the samp_name of the original (or parent) sample from which the current sample was derived. For example, if sample "S01" (the parent sample) was collected at a sampling site and later subsampled into three child samples with samp_names "S01_1", "S01_2", "S01_3", then "S01" is the value for sample_derived_from in each of the child samples. This includes the case of pcr technical replicates.
 Example : S01
-Field type : fixed format ((a list of) samp_name)
-</t>
+Field type : fixed format ((a list of) samp_name)</t>
         </r>
       </text>
     </comment>
@@ -877,12 +828,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (Mandatory unless specified under the term informationWithheld, or samp_category = negative control, positive control, or PCR standard)
 Description : The geographic longitude in decimal degrees using WGS84 datum. Positive values are east of the Greenwich Meridian, negative values are west of it. Legal values lie between -180 and 180, inclusive. The desired minimum number of decimal places is the hundred-thousandth (0.00001) to achieve meter scale resolution.
 Example : -121.17611
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -894,12 +844,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (Mandatory unless specified under the term informationWithheld, or samp_category = negative control, positive control, or PCR standard)
 Description : The geographic latitude in decimal degrees using WGS84 datum. Positive values are north of the Equator, negative values are south of it. Legal values lie between -90 and 90, inclusive. The desired minimum number of decimal places is the hundred-thousandth (0.00001) to achieve meter scale resolution.
 Example : -41.09834
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -911,12 +860,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : The geographical origin of the sample as defined by the country or sea name followed by regions and localities. Country or sea names should be chosen from the INSDC Geographic Location Name List INSDC country list (http://insdc.org/country.html). Fixed format following &lt;country or sea names&gt;:&lt;region&gt;,&lt;locality&gt;. E.g., "USA: Maryland, Bethesda" , "Atlantic Ocean:Charlie Gibbs Fracture Zone"
 Example : USA: Maryland, Bethesda
-Field type : fixed format (&lt;country or sea names&gt;:&lt;region&gt;,&lt;locality&gt;)
-</t>
+Field type : fixed format (&lt;country or sea names&gt;:&lt;region&gt;,&lt;locality&gt;)</t>
         </r>
       </text>
     </comment>
@@ -928,12 +876,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : The date and time of sampling, either as an instance (single point in time) or interval. Must follow ISO 8601 format (yyyy-mm-ddThh:mm:ss). Time zone must be specified after the timestamp (e.g., "2008-01-23T19:23-06:00" in the time zone six hours earlier than UTC, "2008-01-23T19:23Z" at UTC time). In case no exact time is available, the date/time can be right truncated i.e. all of these are valid times: 2008-01-23T19:23:10+00:00; 2008-01-23T19:23:10Z; 2008-01-23; 2008-01; 2008; Except: 2008-01; 2008 all are ISO8601 compliant. A date and time range can be specified using a forward slash (/) to separate the start and end values (e.g., 2008-01-23T19:23-06:00/2008-01-23T19:53-06:00). A duration can also be provided using the eventDurationValue term.
 Example : 2008-01-23T19:23-06:00
-Field type : fixed format (yyyy-mm-ddThh:mm:ss+-hh:mm)
-</t>
+Field type : fixed format (yyyy-mm-ddThh:mm:ss+-hh:mm)</t>
         </r>
       </text>
     </comment>
@@ -945,12 +892,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (Mandatory unless samp_category = negative control, positive control, or PCR standard)
 Description : Major environmental system your sample came from. The systems identified should have a coarse spatial grain, to provide the general environmental context of where the sampling was done. Select from ENVO’s biome class: http://purl.obolibrary.org/obo/ENVO_00000428. Examples include; estuarine biome [ENVO:01000020], tropical moist broadleaf forest biome [ENVO:01000228],
 Example : estuarine biome [ENVO:01000020]
-Field type : fixed format (termLabel [termID])
-</t>
+Field type : fixed format (termLabel [termID])</t>
         </r>
       </text>
     </comment>
@@ -962,12 +908,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (Mandatory unless samp_category = negative control, positive control, or PCR standard)
 Description : The entity or entities which are in your sample or specimen’s local vicinity and which you believe have significant causal influences on your sample. Select from ENVO's layer class: http://purl.obolibrary.org/obo/ENVO_01000281. Examples include;  marine pelagic zone [ENVO:00000208], estuarine coastal surface layer [ENVO:01001302], shrub layer [ENVO:01000336]
 Example : estuarine coastal surface layer [ENVO:01001302]
-Field type : fixed format (termLabel [termID])
-</t>
+Field type : fixed format (termLabel [termID])</t>
         </r>
       </text>
     </comment>
@@ -979,12 +924,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (Mandatory unless samp_category = negative control, positive control, or PCR standard)
 Description : Environmental material or materials (pipe separated) immediately surrounded your sample prior to sampling. Select from ENVO's environmental material class (entity/ continuant/ independent continuant/ material entity/ environmental material): http://purl.obolibrary.org/obo/ENVO_00010483. Examples include; soil [ENVO:00001998], marine sediment [ENVO:03000033], air [ENVO:00002005], sea water [ENVO:00002149], fresh water [ENVO:00002011], tap water [ENVO:00003096], fecal material [ENVO:00002003], digestive tract environment [ENVO:2100002], intestine environment [ENVO:2100002], planktonic material [ENVO:01000063]
 Example : soil [ENVO:00001998]
-Field type : fixed format (termLabel [termID])
-</t>
+Field type : fixed format (termLabel [termID])</t>
         </r>
       </text>
     </comment>
@@ -1217,12 +1161,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Volume or mass of sample or subsamples that was processed for DNA extraction. For example, if 1L of water was collected and filtered, and half of the filter paper was used for DNA extraction, the entries of samp_size and samp_vol_we_dna_ext should be 1L and 500mL respectively. Specify the unit under the term samp_vol_ext_unit.
 Example : 1500.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -1234,12 +1177,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Unit for samp_vol_we_dna_ext
 Example : mL
-Field type : controlled vocabulary (mL | L | mg | g | kg | cm2 | m2 | cm3 | m3 | other:)
-</t>
+Field type : controlled vocabulary (mL | L | mg | g | kg | cm2 | m2 | cm3 | m3 | other:)</t>
         </r>
       </text>
     </comment>
@@ -1251,12 +1193,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : A link to a literature reference, electronic resource or a standard operating procedure (SOP), that describes the material separation to recover the nucleic acid fraction from a sample. If a custom extraction method has been developed and applied to the samples within this dataset, it is Highly recommended to make the SOP available and provide the link here.
 Example : https://www.qiagen.com/us/resources/resourcedetail?id=5a0517a7-711d-4085-8a28-2bb25fab828a&amp;lang=en
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1268,12 +1209,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The name of the extraction kit used to recover the nucleic acid fraction of an input material
 Example : Qiagen PowerSoil Kit
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1285,12 +1225,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A brief, concise identifier for assay with no spaces or special characters, ensuring machine readability. This ID will be used in file names as 'assay_name'.
 Example : MiFish (metabarcoding) / eSERU5 (qPCR)
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1302,12 +1241,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted)
 Description : Detection of the targeted taxon for each biological replicate, based on the specified detection criteria (detailed under the term 'detection_criteria'). Detected = 1, Not detected = 0. For projects employing multiple assays, this term should be specified separately for each assay. The term name should include the assay identifier in the format detected_notDetected_&lt;assay_name&gt; (e.g., detected_notDetected_eSERU5).
 Example : 1
-Field type : Boolean
-</t>
+Field type : Boolean</t>
         </r>
       </text>
     </comment>
@@ -1380,12 +1318,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : An integer uniquely identifying a specific PCR technical replicate within a sample.
 Example : 1
-Field type : integer
-</t>
+Field type : integer</t>
         </r>
       </text>
     </comment>
@@ -1397,12 +1334,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A brief, concise identifier for assay with no spaces or special characters, ensuring machine readability. This ID will be used in file names as 'assay_name'.
 Example : MiFish (metabarcoding) / eSERU5 (qPCR)
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1414,12 +1350,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted)
 Description : PCR plate ID. This identifier is particularly crucial when location-specific standard curves are employed for targeted assay detections, as it ensures a linkage between the standards and the corresponding eDNA samples. If two-step PCR was applied for a metabarcoding approach, enter the second PCR protocol under the term pcr2_* in the library preparation/sequencing section.
 Example : 20240802_pcr1
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1431,12 +1366,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; amp_vis_method = qPCR)
 Description : The number of cycles required for the fluorescent signal to cross a given value threshold above the baseline for each technical replicate. Quantification cycle (Cq), threshold cycle (Ct), crossing point (Cp), and take-off point (TOP) refer to the same value from the real-time instrument. Use of quantification cycle (Cq), is preferable according to the RDML (Real-Time PCR Data Markup Language) data standard (http://www.rdml.org). Use "NA" (not zero) to indicate no amplification occurred. Unit = Cycle
 Example : 37.9450950622558
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -1458,12 +1392,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : An integer uniquely identifying a specific PCR technical replicate within a sample.
 Example : 1
-Field type : integer
-</t>
+Field type : integer</t>
         </r>
       </text>
     </comment>
@@ -1475,12 +1408,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A brief, concise identifier for assay with no spaces or special characters, ensuring machine readability. This ID will be used in file names as 'assay_name'.
 Example : MiFish (metabarcoding) / eSERU5 (qPCR)
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1492,12 +1424,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted)
 Description : PCR plate ID. This identifier is particularly crucial when location-specific standard curves are employed for targeted assay detections, as it ensures a linkage between the standards and the corresponding eDNA samples. If two-step PCR was applied for a metabarcoding approach, enter the second PCR protocol under the term pcr2_* in the library preparation/sequencing section.
 Example : 20240802_pcr1
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1509,12 +1440,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (if samp_category = PCR standard)
 Description : Input quantity of qPCR standard DNA
 Example : 2500.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -1526,12 +1456,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (if samp_category = PCR standard)
 Description : Unit for input quantity of qPCR standard DNA
 Example : NA
-Field type : controlled vocabulary (copies/reaction | copies/µL of DNA extract | copies/µL of reaction | ng/reaction | ng/µL of DNA extract | ng/µL of reaction | other:)
-</t>
+Field type : controlled vocabulary (copies/reaction | copies/µL of DNA extract | copies/µL of reaction | ng/reaction | ng/µL of DNA extract | ng/µL of reaction | other:)</t>
         </r>
       </text>
     </comment>
@@ -1543,12 +1472,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted &amp; amp_vis_method = qPCR)
 Description : The number of cycles required for the fluorescent signal to cross a given value threshold above the baseline for each technical replicate. Quantification cycle (Cq), threshold cycle (Ct), crossing point (Cp), and take-off point (TOP) refer to the same value from the real-time instrument. Use of quantification cycle (Cq), is preferable according to the RDML (Real-Time PCR Data Markup Language) data standard (http://www.rdml.org). Use "NA" (not zero) to indicate no amplification occurred. Unit = Cycle
 Example : 37.9450950622558
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -1560,12 +1488,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : qPCR amplification efficiency calculated from slope. Unit = %
 Example : 95.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -1577,12 +1504,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : R-squared value of a qPCR standard curve. This shall be specific to each pcr_plate_id.
 Example : 0.9867
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -1604,12 +1530,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : Number of detection using the eLow Quant approach (described in DOI: 10.1002/edn3.220)
 Example : 2
-Field type : integer
-</t>
+Field type : integer</t>
         </r>
       </text>
     </comment>
@@ -1631,12 +1556,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory
 Description : A brief, concise identifier for assay with no spaces or special characters, ensuring machine readability. This ID will be used in file names as 'assay_name'.
 Example : MiFish (metabarcoding) / eSERU5 (qPCR)
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1648,12 +1572,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = targeted)
 Description : PCR plate ID. This identifier is particularly crucial when location-specific standard curves are employed for targeted assay detections, as it ensures a linkage between the standards and the corresponding eDNA samples. If two-step PCR was applied for a metabarcoding approach, enter the second PCR protocol under the term pcr2_* in the library preparation/sequencing section.
 Example : 20240802_pcr1
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1665,12 +1588,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = metabarcoding)
 Description : An identifier of a library (an amplicon of a sample with unique MIDs)
 Example : S01_MiSeq_run20230922
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1682,12 +1604,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = metabarcoding)
 Description : A brief, concise identifier for sequencing run with no spaces or special characters, ensuring machine readability. This ID will be used in file names as 'seq_run_id'.
 Example : run20230922
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1709,12 +1630,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = metabarcoding)
 Description : The DNA sequence
 Example : GGTGTTTAAATTTCGGTCTGTAAGAAGTATTGTAATCCCAGCCGCTAGGACTGGAAGGGAAAGAAGGAGAAGGACAGCTGTAATTAGCACGGCTCAGACAAACAAGGGTGTCTGGTATTGGGAAATAGCTGGGGGTTTCATGTTAATAATTGTGGTAATAAAATTGATAGCACCAAGGATTGAAGAGACCCCGGCTAGGTGGAGAGAA
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1726,12 +1646,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The full scientific name of the genus and species
 Example : Lutjanus erythropterus
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1743,12 +1662,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The taxonomic rank of the most specific name in the scientificName
 Example : genus
-Field type : controlled vocabulary (kingdom | phylum | class | order | family | genus | species | other:)
-</t>
+Field type : controlled vocabulary (kingdom | phylum | class | order | family | genus | species | other:)</t>
         </r>
       </text>
     </comment>
@@ -1760,12 +1678,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : An identifier for the assigned taxon (or taxa in the case of multiple hits). May be a global unique identifier or an identifier specific to the data set.
 Example : 218797.0
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1777,12 +1694,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The taxonomy database corresponding to taxonID.
 Example : NCBI
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1804,12 +1720,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Mandatory (If assay_type = metabarcoding)
 Description : The DNA sequence
 Example : GGTGTTTAAATTTCGGTCTGTAAGAAGTATTGTAATCCCAGCCGCTAGGACTGGAAGGGAAAGAAGGAGAAGGACAGCTGTAATTAGCACGGCTCAGACAAACAAGGGTGTCTGGTATTGGGAAATAGCTGGGGGTTTCATGTTAATAATTGTGGTAATAAAATTGATAGCACCAAGGATTGAAGAGACCCCGGCTAGGTGGAGAGAA
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1821,12 +1736,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The full scientific name of the kingdom
 Example : Animalia
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1838,12 +1752,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The full scientific name of the phylum or division
 Example : Chordata
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1855,12 +1768,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The full scientific name of the class
 Example : Actinopterygii
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1872,12 +1784,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The full scientific name of the order
 Example : Perciformes
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1889,12 +1800,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The full scientific name of the family
 Example : Lutjanidae
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1906,12 +1816,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The full scientific name of the genus
 Example : Lutjanus
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1923,12 +1832,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The name of the first or species epithet of the scientificName.
 Example : erythropterus
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1940,12 +1848,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The full scientific name of the genus and species
 Example : Lutjanus erythropterus
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1957,12 +1864,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The authorship information for the scientificName
 Example : Bloch, 1790
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -1974,12 +1880,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The taxonomic rank of the most specific name in the scientificName
 Example : genus
-Field type : controlled vocabulary (kingdom | phylum | class | order | family | genus | species | other:)
-</t>
+Field type : controlled vocabulary (kingdom | phylum | class | order | family | genus | species | other:)</t>
         </r>
       </text>
     </comment>
@@ -1991,12 +1896,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : An identifier for the assigned taxon (or taxa in the case of multiple hits). May be a global unique identifier or an identifier specific to the data set.
 Example : 218797.0
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -2008,12 +1912,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Highly recommended
 Description : The taxonomy database corresponding to taxonID.
 Example : NCBI
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -2025,12 +1928,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : Accession ID of the best matching sequence from a reference database
 Example : MG002616.1
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -2042,12 +1944,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : Reference database (i.e. sequences not generated as part of the current study) of the best matching sequence (accesssion_id)
 Example : NCBI
-Field type : free text
-</t>
+Field type : free text</t>
         </r>
       </text>
     </comment>
@@ -2059,12 +1960,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The percentage of sequence identity between a query sequence obtained from eDNA and a reference sequence in a database. If multiple species were assigned to one ASV/OTU, a range can be entered separated by  "-" (e.g., 98.7-99.2).
 Example : 99.8
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -2076,12 +1976,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : The percentage coverage of the query sequence that aligns with a reference sequence in a database. If multiple species were assigned to one ASV/OTU, a range can be entered separated by  "-" (e.g., 98.7-99.2).  Unit = %
 Example : 100.0
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -2093,12 +1992,11 @@
             <color indexed="8"/>
             <rFont val="Helvetica Neue"/>
           </rPr>
-          <t xml:space="preserve">Imported Author:
+          <t>Imported Author:
 Requirement level : Recommended
 Description : Confidence score for the taxonomic assignment, such as from bootstrapping. If multiple species were assigned to one ASV/OTU, a range can be entered separated by  "-" (e.g., 0.996-0.998)
 Example : 0.997
-Field type : numeric
-</t>
+Field type : numeric</t>
         </r>
       </text>
     </comment>
@@ -2107,18 +2005,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="425">
   <si>
     <t>The templates were generated using the FAIR eDNA checklist version of;</t>
   </si>
   <si>
-    <t>FAIRe_checklist_v1.0.2.xlsx</t>
-  </si>
-  <si>
     <t>Date/Time generated;</t>
-  </si>
-  <si>
-    <t>2025-07-02T11:34:09+08:00</t>
   </si>
   <si>
     <t>Note: This template includes most data components and terms from the FAIR eDNA checklist and Required Neotoma fields.</t>
@@ -3434,7 +3326,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -3473,35 +3365,35 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right/>
       <top/>
@@ -3511,37 +3403,37 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3549,42 +3441,42 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -3595,71 +3487,74 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -3668,13 +3563,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -3683,7 +3572,13 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -3695,13 +3590,13 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -3721,12 +3616,12 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ffe26b0a"/>
       <rgbColor rgb="ffffcc00"/>
       <rgbColor rgb="ffffff99"/>
       <rgbColor rgb="ffccff99"/>
-      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -3957,12 +3852,12 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -3994,10 +3889,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -4236,12 +4131,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -4545,10 +4440,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -4808,9 +4703,7 @@
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" t="s" s="2">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -4825,7 +4718,7 @@
     </row>
     <row r="4" ht="13.55" customHeight="1">
       <c r="A4" t="s" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4833,9 +4726,7 @@
       <c r="E4" s="3"/>
     </row>
     <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" t="s" s="2">
-        <v>3</v>
-      </c>
+      <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -4850,7 +4741,7 @@
     </row>
     <row r="7" ht="13.55" customHeight="1">
       <c r="A7" t="s" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -4866,7 +4757,7 @@
     </row>
     <row r="9" ht="13.55" customHeight="1">
       <c r="A9" t="s" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4875,7 +4766,7 @@
     </row>
     <row r="10" ht="13.55" customHeight="1">
       <c r="A10" t="s" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="3"/>
@@ -4884,7 +4775,7 @@
     </row>
     <row r="11" ht="13.55" customHeight="1">
       <c r="A11" t="s" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="3"/>
@@ -4893,7 +4784,7 @@
     </row>
     <row r="12" ht="13.55" customHeight="1">
       <c r="A12" t="s" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="3"/>
@@ -4902,7 +4793,7 @@
     </row>
     <row r="13" ht="13.55" customHeight="1">
       <c r="A13" t="s" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="3"/>
@@ -4923,198 +4814,198 @@
   <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="34" customWidth="1"/>
-    <col min="2" max="2" width="13.6719" style="34" customWidth="1"/>
-    <col min="3" max="8" width="8.85156" style="34" customWidth="1"/>
-    <col min="9" max="9" width="13.8516" style="34" customWidth="1"/>
-    <col min="10" max="10" width="14" style="34" customWidth="1"/>
-    <col min="11" max="11" width="23.6719" style="34" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="34" customWidth="1"/>
-    <col min="13" max="13" width="8.85156" style="34" customWidth="1"/>
-    <col min="14" max="14" width="11.1719" style="34" customWidth="1"/>
-    <col min="15" max="15" width="12.1719" style="34" customWidth="1"/>
-    <col min="16" max="16" width="18.8516" style="34" customWidth="1"/>
-    <col min="17" max="17" width="14.3516" style="34" customWidth="1"/>
-    <col min="18" max="18" width="19.6719" style="34" customWidth="1"/>
-    <col min="19" max="19" width="16.3516" style="34" customWidth="1"/>
-    <col min="20" max="16384" width="14.5" style="34" customWidth="1"/>
+    <col min="1" max="1" width="23.5" style="35" customWidth="1"/>
+    <col min="2" max="2" width="13.6719" style="35" customWidth="1"/>
+    <col min="3" max="8" width="8.85156" style="35" customWidth="1"/>
+    <col min="9" max="9" width="13.8516" style="35" customWidth="1"/>
+    <col min="10" max="10" width="14" style="35" customWidth="1"/>
+    <col min="11" max="11" width="23.6719" style="35" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="35" customWidth="1"/>
+    <col min="13" max="13" width="8.85156" style="35" customWidth="1"/>
+    <col min="14" max="14" width="11.1719" style="35" customWidth="1"/>
+    <col min="15" max="15" width="12.1719" style="35" customWidth="1"/>
+    <col min="16" max="16" width="18.8516" style="35" customWidth="1"/>
+    <col min="17" max="17" width="14.3516" style="35" customWidth="1"/>
+    <col min="18" max="18" width="19.6719" style="35" customWidth="1"/>
+    <col min="19" max="19" width="16.3516" style="35" customWidth="1"/>
+    <col min="20" max="16384" width="14.5" style="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="20">
+        <v>367</v>
+      </c>
+      <c r="B1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s" s="23">
         <v>369</v>
       </c>
-      <c r="B1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s" s="23">
-        <v>371</v>
-      </c>
       <c r="D1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="I1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Q1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="R1" t="s" s="23">
-        <v>371</v>
-      </c>
-      <c r="S1" t="s" s="35">
-        <v>371</v>
+        <v>369</v>
+      </c>
+      <c r="S1" t="s" s="36">
+        <v>369</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="C2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="D2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="E2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="F2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="G2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="H2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="I2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="J2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="K2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="L2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="M2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="N2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="O2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="P2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="Q2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="R2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="S2" t="s" s="25">
-        <v>414</v>
+        <v>370</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="C2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="D2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="E2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="F2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="G2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="H2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="I2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="J2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="K2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="L2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="M2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="N2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="O2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="P2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="Q2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="R2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="S2" t="s" s="26">
+        <v>412</v>
       </c>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="12">
+        <v>417</v>
+      </c>
+      <c r="B3" t="s" s="12">
+        <v>413</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>317</v>
+      </c>
+      <c r="D3" t="s" s="12">
+        <v>318</v>
+      </c>
+      <c r="E3" t="s" s="12">
+        <v>319</v>
+      </c>
+      <c r="F3" t="s" s="12">
+        <v>320</v>
+      </c>
+      <c r="G3" t="s" s="12">
+        <v>321</v>
+      </c>
+      <c r="H3" t="s" s="12">
+        <v>322</v>
+      </c>
+      <c r="I3" t="s" s="12">
+        <v>418</v>
+      </c>
+      <c r="J3" t="s" s="12">
+        <v>414</v>
+      </c>
+      <c r="K3" t="s" s="12">
         <v>419</v>
       </c>
-      <c r="B3" t="s" s="12">
+      <c r="L3" t="s" s="12">
+        <v>315</v>
+      </c>
+      <c r="M3" t="s" s="12">
         <v>415</v>
       </c>
-      <c r="C3" t="s" s="12">
-        <v>319</v>
-      </c>
-      <c r="D3" t="s" s="12">
-        <v>320</v>
-      </c>
-      <c r="E3" t="s" s="12">
-        <v>321</v>
-      </c>
-      <c r="F3" t="s" s="12">
-        <v>322</v>
-      </c>
-      <c r="G3" t="s" s="12">
-        <v>323</v>
-      </c>
-      <c r="H3" t="s" s="12">
-        <v>324</v>
-      </c>
-      <c r="I3" t="s" s="12">
+      <c r="N3" t="s" s="12">
+        <v>416</v>
+      </c>
+      <c r="O3" t="s" s="12">
         <v>420</v>
       </c>
-      <c r="J3" t="s" s="12">
-        <v>416</v>
-      </c>
-      <c r="K3" t="s" s="12">
+      <c r="P3" t="s" s="12">
         <v>421</v>
       </c>
-      <c r="L3" t="s" s="12">
-        <v>317</v>
-      </c>
-      <c r="M3" t="s" s="12">
-        <v>417</v>
-      </c>
-      <c r="N3" t="s" s="12">
-        <v>418</v>
-      </c>
-      <c r="O3" t="s" s="12">
+      <c r="Q3" t="s" s="12">
         <v>422</v>
       </c>
-      <c r="P3" t="s" s="12">
+      <c r="R3" t="s" s="12">
         <v>423</v>
       </c>
-      <c r="Q3" t="s" s="12">
+      <c r="S3" t="s" s="12">
         <v>424</v>
-      </c>
-      <c r="R3" t="s" s="12">
-        <v>425</v>
-      </c>
-      <c r="S3" t="s" s="12">
-        <v>426</v>
       </c>
     </row>
     <row r="4" ht="13.55" customHeight="1">
@@ -5295,600 +5186,600 @@
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="11">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s" s="12">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s" s="12">
         <v>10</v>
       </c>
-      <c r="B1" t="s" s="12">
+      <c r="D1" t="s" s="12">
         <v>11</v>
-      </c>
-      <c r="C1" t="s" s="12">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s" s="12">
-        <v>13</v>
       </c>
       <c r="E1" s="3"/>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="5">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s" s="13">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s" s="12">
         <v>14</v>
-      </c>
-      <c r="B2" t="s" s="13">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s" s="12">
-        <v>16</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s" s="13">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s" s="12">
         <v>15</v>
-      </c>
-      <c r="C3" t="s" s="12">
-        <v>17</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" ht="13.55" customHeight="1">
       <c r="A4" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" ht="13.55" customHeight="1">
       <c r="A5" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s" s="12">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" ht="13.55" customHeight="1">
       <c r="A6" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" ht="13.55" customHeight="1">
       <c r="A7" t="s" s="7">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s" s="13">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s" s="12">
         <v>20</v>
-      </c>
-      <c r="B7" t="s" s="13">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s" s="12">
-        <v>22</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" ht="13.55" customHeight="1">
       <c r="A8" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s" s="13">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s" s="12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" ht="13.55" customHeight="1">
       <c r="A9" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s" s="13">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s" s="12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="12">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s" s="13">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s" s="12">
         <v>26</v>
-      </c>
-      <c r="C11" t="s" s="12">
-        <v>28</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s" s="12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s" s="12">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s" s="12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s" s="12">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s" s="12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s" s="12">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s" s="12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s" s="12">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s" s="12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s" s="12">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s" s="12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s" s="12">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s" s="12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s" s="12">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s" s="12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s" s="12">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s" s="12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s" s="13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s" s="12">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s" s="13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s" s="12">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s" s="13">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s" s="12">
         <v>48</v>
-      </c>
-      <c r="C32" t="s" s="12">
-        <v>50</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s" s="13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s" s="12">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s" s="13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s" s="12">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s" s="13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s" s="12">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s" s="13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s" s="12">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" t="s" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s" s="13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s" s="12">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s" s="13">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s" s="12">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s" s="13">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s" s="12">
         <v>56</v>
-      </c>
-      <c r="C39" t="s" s="12">
-        <v>58</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B40" t="s" s="13">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s" s="12">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s" s="13">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s" s="12">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B42" t="s" s="13">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s" s="12">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s" s="13">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s" s="12">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B44" t="s" s="13">
+        <v>60</v>
+      </c>
+      <c r="C44" t="s" s="12">
         <v>62</v>
-      </c>
-      <c r="C44" t="s" s="12">
-        <v>64</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" t="s" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s" s="13">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s" s="12">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" t="s" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s" s="13">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s" s="12">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -5962,126 +5853,126 @@
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s" s="16">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s" s="16">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s" s="16">
         <v>67</v>
       </c>
-      <c r="C1" t="s" s="16">
+      <c r="E1" t="s" s="16">
         <v>68</v>
       </c>
-      <c r="D1" t="s" s="16">
+      <c r="F1" t="s" s="16">
         <v>69</v>
       </c>
-      <c r="E1" t="s" s="16">
+      <c r="G1" t="s" s="16">
         <v>70</v>
       </c>
-      <c r="F1" t="s" s="16">
+      <c r="H1" t="s" s="16">
         <v>71</v>
       </c>
-      <c r="G1" t="s" s="16">
+      <c r="I1" t="s" s="16">
         <v>72</v>
       </c>
-      <c r="H1" t="s" s="16">
+      <c r="J1" t="s" s="16">
         <v>73</v>
       </c>
-      <c r="I1" t="s" s="16">
+      <c r="K1" t="s" s="16">
         <v>74</v>
       </c>
-      <c r="J1" t="s" s="16">
+      <c r="L1" t="s" s="16">
         <v>75</v>
       </c>
-      <c r="K1" t="s" s="16">
+      <c r="M1" t="s" s="16">
         <v>76</v>
       </c>
-      <c r="L1" t="s" s="16">
+      <c r="N1" t="s" s="16">
         <v>77</v>
       </c>
-      <c r="M1" t="s" s="16">
+      <c r="O1" t="s" s="16">
         <v>78</v>
       </c>
-      <c r="N1" t="s" s="16">
+      <c r="P1" t="s" s="16">
         <v>79</v>
       </c>
-      <c r="O1" t="s" s="16">
+      <c r="Q1" t="s" s="16">
         <v>80</v>
       </c>
-      <c r="P1" t="s" s="16">
+      <c r="R1" t="s" s="16">
         <v>81</v>
       </c>
-      <c r="Q1" t="s" s="16">
+      <c r="S1" t="s" s="16">
         <v>82</v>
       </c>
-      <c r="R1" t="s" s="16">
+      <c r="T1" t="s" s="16">
         <v>83</v>
       </c>
-      <c r="S1" t="s" s="16">
+      <c r="U1" t="s" s="16">
         <v>84</v>
       </c>
-      <c r="T1" t="s" s="16">
+      <c r="V1" t="s" s="16">
         <v>85</v>
       </c>
-      <c r="U1" t="s" s="16">
+      <c r="W1" t="s" s="16">
         <v>86</v>
       </c>
-      <c r="V1" t="s" s="16">
+      <c r="X1" t="s" s="16">
         <v>87</v>
       </c>
-      <c r="W1" t="s" s="16">
+      <c r="Y1" t="s" s="16">
         <v>88</v>
       </c>
-      <c r="X1" t="s" s="16">
+      <c r="Z1" t="s" s="16">
         <v>89</v>
       </c>
-      <c r="Y1" t="s" s="16">
+      <c r="AA1" t="s" s="16">
         <v>90</v>
       </c>
-      <c r="Z1" t="s" s="16">
+      <c r="AB1" t="s" s="16">
         <v>91</v>
       </c>
-      <c r="AA1" t="s" s="16">
+      <c r="AC1" t="s" s="16">
         <v>92</v>
       </c>
-      <c r="AB1" t="s" s="16">
+      <c r="AD1" t="s" s="16">
         <v>93</v>
       </c>
-      <c r="AC1" t="s" s="16">
+      <c r="AE1" t="s" s="16">
         <v>94</v>
       </c>
-      <c r="AD1" t="s" s="16">
+      <c r="AF1" t="s" s="16">
         <v>95</v>
       </c>
-      <c r="AE1" t="s" s="16">
+      <c r="AG1" t="s" s="16">
         <v>96</v>
-      </c>
-      <c r="AF1" t="s" s="16">
-        <v>97</v>
-      </c>
-      <c r="AG1" t="s" s="16">
-        <v>98</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="16">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s" s="16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" s="17">
         <v>3</v>
       </c>
       <c r="E2" t="s" s="16">
+        <v>99</v>
+      </c>
+      <c r="F2" t="s" s="16">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s" s="16">
         <v>101</v>
-      </c>
-      <c r="F2" t="s" s="16">
-        <v>102</v>
-      </c>
-      <c r="G2" t="s" s="16">
-        <v>103</v>
       </c>
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
@@ -6112,22 +6003,22 @@
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="16">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D3" s="17">
         <v>2</v>
       </c>
       <c r="E3" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G3" s="18"/>
       <c r="H3" s="18"/>
@@ -6159,22 +6050,22 @@
     </row>
     <row r="4" ht="13.55" customHeight="1">
       <c r="A4" t="s" s="16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D4" s="17">
         <v>2</v>
       </c>
       <c r="E4" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F4" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
@@ -6206,31 +6097,31 @@
     </row>
     <row r="5" ht="13.55" customHeight="1">
       <c r="A5" t="s" s="16">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s" s="16">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D5" s="17">
         <v>5</v>
       </c>
       <c r="E5" t="s" s="16">
+        <v>108</v>
+      </c>
+      <c r="F5" t="s" s="16">
+        <v>109</v>
+      </c>
+      <c r="G5" t="s" s="16">
         <v>110</v>
       </c>
-      <c r="F5" t="s" s="16">
+      <c r="H5" t="s" s="16">
         <v>111</v>
       </c>
-      <c r="G5" t="s" s="16">
-        <v>112</v>
-      </c>
-      <c r="H5" t="s" s="16">
-        <v>113</v>
-      </c>
       <c r="I5" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -6259,34 +6150,34 @@
     </row>
     <row r="6" ht="13.55" customHeight="1">
       <c r="A6" t="s" s="16">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s" s="16">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D6" s="17">
         <v>6</v>
       </c>
       <c r="E6" t="s" s="16">
+        <v>114</v>
+      </c>
+      <c r="F6" t="s" s="16">
+        <v>115</v>
+      </c>
+      <c r="G6" t="s" s="16">
         <v>116</v>
       </c>
-      <c r="F6" t="s" s="16">
+      <c r="H6" t="s" s="16">
         <v>117</v>
       </c>
-      <c r="G6" t="s" s="16">
+      <c r="I6" t="s" s="16">
         <v>118</v>
       </c>
-      <c r="H6" t="s" s="16">
-        <v>119</v>
-      </c>
-      <c r="I6" t="s" s="16">
-        <v>120</v>
-      </c>
       <c r="J6" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -6314,28 +6205,28 @@
     </row>
     <row r="7" ht="13.55" customHeight="1">
       <c r="A7" t="s" s="16">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s" s="16">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D7" s="17">
         <v>4</v>
       </c>
       <c r="E7" t="s" s="16">
+        <v>121</v>
+      </c>
+      <c r="F7" t="s" s="16">
+        <v>122</v>
+      </c>
+      <c r="G7" t="s" s="16">
         <v>123</v>
       </c>
-      <c r="F7" t="s" s="16">
-        <v>124</v>
-      </c>
-      <c r="G7" t="s" s="16">
-        <v>125</v>
-      </c>
       <c r="H7" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
@@ -6365,40 +6256,40 @@
     </row>
     <row r="8" ht="13.55" customHeight="1">
       <c r="A8" t="s" s="16">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s" s="16">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D8" s="17">
         <v>8</v>
       </c>
       <c r="E8" t="s" s="16">
+        <v>126</v>
+      </c>
+      <c r="F8" t="s" s="16">
+        <v>127</v>
+      </c>
+      <c r="G8" t="s" s="16">
         <v>128</v>
       </c>
-      <c r="F8" t="s" s="16">
+      <c r="H8" t="s" s="16">
         <v>129</v>
       </c>
-      <c r="G8" t="s" s="16">
+      <c r="I8" t="s" s="16">
         <v>130</v>
       </c>
-      <c r="H8" t="s" s="16">
+      <c r="J8" t="s" s="16">
         <v>131</v>
       </c>
-      <c r="I8" t="s" s="16">
+      <c r="K8" t="s" s="16">
         <v>132</v>
       </c>
-      <c r="J8" t="s" s="16">
-        <v>133</v>
-      </c>
-      <c r="K8" t="s" s="16">
-        <v>134</v>
-      </c>
       <c r="L8" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
@@ -6424,22 +6315,22 @@
     </row>
     <row r="9" ht="13.55" customHeight="1">
       <c r="A9" t="s" s="16">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D9" s="17">
         <v>2</v>
       </c>
       <c r="E9" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F9" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
@@ -6471,46 +6362,46 @@
     </row>
     <row r="10" ht="13.55" customHeight="1">
       <c r="A10" t="s" s="16">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s" s="16">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D10" s="17">
         <v>10</v>
       </c>
       <c r="E10" t="s" s="16">
+        <v>136</v>
+      </c>
+      <c r="F10" t="s" s="16">
+        <v>137</v>
+      </c>
+      <c r="G10" t="s" s="16">
         <v>138</v>
       </c>
-      <c r="F10" t="s" s="16">
+      <c r="H10" t="s" s="16">
         <v>139</v>
       </c>
-      <c r="G10" t="s" s="16">
+      <c r="I10" t="s" s="16">
         <v>140</v>
       </c>
-      <c r="H10" t="s" s="16">
+      <c r="J10" t="s" s="16">
         <v>141</v>
       </c>
-      <c r="I10" t="s" s="16">
+      <c r="K10" t="s" s="16">
         <v>142</v>
       </c>
-      <c r="J10" t="s" s="16">
+      <c r="L10" t="s" s="16">
         <v>143</v>
       </c>
-      <c r="K10" t="s" s="16">
+      <c r="M10" t="s" s="16">
         <v>144</v>
       </c>
-      <c r="L10" t="s" s="16">
-        <v>145</v>
-      </c>
-      <c r="M10" t="s" s="16">
-        <v>146</v>
-      </c>
       <c r="N10" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O10" s="18"/>
       <c r="P10" s="18"/>
@@ -6534,34 +6425,34 @@
     </row>
     <row r="11" ht="13.55" customHeight="1">
       <c r="A11" t="s" s="16">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s" s="16">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D11" s="17">
         <v>6</v>
       </c>
       <c r="E11" t="s" s="16">
+        <v>147</v>
+      </c>
+      <c r="F11" t="s" s="16">
+        <v>148</v>
+      </c>
+      <c r="G11" t="s" s="16">
         <v>149</v>
       </c>
-      <c r="F11" t="s" s="16">
+      <c r="H11" t="s" s="16">
         <v>150</v>
       </c>
-      <c r="G11" t="s" s="16">
+      <c r="I11" t="s" s="16">
         <v>151</v>
       </c>
-      <c r="H11" t="s" s="16">
-        <v>152</v>
-      </c>
-      <c r="I11" t="s" s="16">
-        <v>153</v>
-      </c>
       <c r="J11" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
@@ -6589,22 +6480,22 @@
     </row>
     <row r="12" ht="13.55" customHeight="1">
       <c r="A12" t="s" s="16">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D12" s="17">
         <v>2</v>
       </c>
       <c r="E12" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
@@ -6636,37 +6527,37 @@
     </row>
     <row r="13" ht="13.55" customHeight="1">
       <c r="A13" t="s" s="16">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s" s="16">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D13" s="17">
         <v>7</v>
       </c>
       <c r="E13" t="s" s="16">
+        <v>155</v>
+      </c>
+      <c r="F13" t="s" s="16">
+        <v>156</v>
+      </c>
+      <c r="G13" t="s" s="16">
         <v>157</v>
       </c>
-      <c r="F13" t="s" s="16">
+      <c r="H13" t="s" s="16">
         <v>158</v>
       </c>
-      <c r="G13" t="s" s="16">
+      <c r="I13" t="s" s="16">
         <v>159</v>
       </c>
-      <c r="H13" t="s" s="16">
+      <c r="J13" t="s" s="16">
         <v>160</v>
       </c>
-      <c r="I13" t="s" s="16">
-        <v>161</v>
-      </c>
-      <c r="J13" t="s" s="16">
-        <v>162</v>
-      </c>
       <c r="K13" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
@@ -6693,40 +6584,40 @@
     </row>
     <row r="14" ht="13.55" customHeight="1">
       <c r="A14" t="s" s="16">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s" s="16">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D14" s="17">
         <v>8</v>
       </c>
       <c r="E14" t="s" s="16">
+        <v>163</v>
+      </c>
+      <c r="F14" t="s" s="16">
+        <v>164</v>
+      </c>
+      <c r="G14" t="s" s="16">
         <v>165</v>
       </c>
-      <c r="F14" t="s" s="16">
+      <c r="H14" t="s" s="16">
         <v>166</v>
       </c>
-      <c r="G14" t="s" s="16">
+      <c r="I14" t="s" s="16">
         <v>167</v>
       </c>
-      <c r="H14" t="s" s="16">
+      <c r="J14" t="s" s="16">
         <v>168</v>
       </c>
-      <c r="I14" t="s" s="16">
+      <c r="K14" t="s" s="16">
         <v>169</v>
       </c>
-      <c r="J14" t="s" s="16">
-        <v>170</v>
-      </c>
-      <c r="K14" t="s" s="16">
-        <v>171</v>
-      </c>
       <c r="L14" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
@@ -6752,28 +6643,28 @@
     </row>
     <row r="15" ht="13.55" customHeight="1">
       <c r="A15" t="s" s="16">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s" s="16">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D15" s="17">
         <v>4</v>
       </c>
       <c r="E15" t="s" s="16">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F15" t="s" s="16">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G15" t="s" s="16">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H15" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
@@ -6803,34 +6694,34 @@
     </row>
     <row r="16" ht="13.55" customHeight="1">
       <c r="A16" t="s" s="16">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s" s="16">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D16" s="17">
         <v>6</v>
       </c>
       <c r="E16" t="s" s="16">
+        <v>147</v>
+      </c>
+      <c r="F16" t="s" s="16">
+        <v>148</v>
+      </c>
+      <c r="G16" t="s" s="16">
         <v>149</v>
       </c>
-      <c r="F16" t="s" s="16">
+      <c r="H16" t="s" s="16">
         <v>150</v>
       </c>
-      <c r="G16" t="s" s="16">
+      <c r="I16" t="s" s="16">
         <v>151</v>
       </c>
-      <c r="H16" t="s" s="16">
-        <v>152</v>
-      </c>
-      <c r="I16" t="s" s="16">
-        <v>153</v>
-      </c>
       <c r="J16" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
@@ -6858,46 +6749,46 @@
     </row>
     <row r="17" ht="13.55" customHeight="1">
       <c r="A17" t="s" s="16">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s" s="16">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D17" s="17">
         <v>10</v>
       </c>
       <c r="E17" t="s" s="16">
+        <v>136</v>
+      </c>
+      <c r="F17" t="s" s="16">
+        <v>137</v>
+      </c>
+      <c r="G17" t="s" s="16">
         <v>138</v>
       </c>
-      <c r="F17" t="s" s="16">
+      <c r="H17" t="s" s="16">
         <v>139</v>
       </c>
-      <c r="G17" t="s" s="16">
+      <c r="I17" t="s" s="16">
         <v>140</v>
       </c>
-      <c r="H17" t="s" s="16">
+      <c r="J17" t="s" s="16">
         <v>141</v>
       </c>
-      <c r="I17" t="s" s="16">
+      <c r="K17" t="s" s="16">
         <v>142</v>
       </c>
-      <c r="J17" t="s" s="16">
+      <c r="L17" t="s" s="16">
         <v>143</v>
       </c>
-      <c r="K17" t="s" s="16">
+      <c r="M17" t="s" s="16">
         <v>144</v>
       </c>
-      <c r="L17" t="s" s="16">
-        <v>145</v>
-      </c>
-      <c r="M17" t="s" s="16">
-        <v>146</v>
-      </c>
       <c r="N17" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O17" s="18"/>
       <c r="P17" s="18"/>
@@ -6921,34 +6812,34 @@
     </row>
     <row r="18" ht="13.55" customHeight="1">
       <c r="A18" t="s" s="16">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s" s="16">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D18" s="17">
         <v>6</v>
       </c>
       <c r="E18" t="s" s="16">
+        <v>178</v>
+      </c>
+      <c r="F18" t="s" s="16">
+        <v>179</v>
+      </c>
+      <c r="G18" t="s" s="16">
         <v>180</v>
       </c>
-      <c r="F18" t="s" s="16">
+      <c r="H18" t="s" s="16">
         <v>181</v>
       </c>
-      <c r="G18" t="s" s="16">
+      <c r="I18" t="s" s="16">
         <v>182</v>
       </c>
-      <c r="H18" t="s" s="16">
-        <v>183</v>
-      </c>
-      <c r="I18" t="s" s="16">
-        <v>184</v>
-      </c>
       <c r="J18" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
@@ -6976,37 +6867,37 @@
     </row>
     <row r="19" ht="13.55" customHeight="1">
       <c r="A19" t="s" s="16">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s" s="16">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D19" s="17">
         <v>7</v>
       </c>
       <c r="E19" t="s" s="16">
+        <v>185</v>
+      </c>
+      <c r="F19" t="s" s="16">
+        <v>186</v>
+      </c>
+      <c r="G19" t="s" s="16">
         <v>187</v>
       </c>
-      <c r="F19" t="s" s="16">
+      <c r="H19" t="s" s="16">
         <v>188</v>
       </c>
-      <c r="G19" t="s" s="16">
+      <c r="I19" t="s" s="16">
         <v>189</v>
       </c>
-      <c r="H19" t="s" s="16">
+      <c r="J19" t="s" s="16">
         <v>190</v>
       </c>
-      <c r="I19" t="s" s="16">
-        <v>191</v>
-      </c>
-      <c r="J19" t="s" s="16">
-        <v>192</v>
-      </c>
       <c r="K19" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
@@ -7033,22 +6924,22 @@
     </row>
     <row r="20" ht="13.55" customHeight="1">
       <c r="A20" t="s" s="16">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D20" s="17">
         <v>2</v>
       </c>
       <c r="E20" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F20" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
@@ -7080,25 +6971,25 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" t="s" s="16">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s" s="16">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D21" s="17">
         <v>3</v>
       </c>
       <c r="E21" t="s" s="16">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F21" t="s" s="16">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G21" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
@@ -7129,22 +7020,22 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" t="s" s="16">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D22" s="17">
         <v>2</v>
       </c>
       <c r="E22" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
@@ -7176,22 +7067,22 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" t="s" s="16">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D23" s="17">
         <v>2</v>
       </c>
       <c r="E23" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
@@ -7223,135 +7114,135 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" t="s" s="16">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s" s="16">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D24" s="17">
         <v>29</v>
       </c>
       <c r="E24" t="s" s="16">
+        <v>198</v>
+      </c>
+      <c r="F24" t="s" s="16">
+        <v>199</v>
+      </c>
+      <c r="G24" t="s" s="16">
         <v>200</v>
       </c>
-      <c r="F24" t="s" s="16">
+      <c r="H24" t="s" s="16">
         <v>201</v>
       </c>
-      <c r="G24" t="s" s="16">
+      <c r="I24" t="s" s="16">
         <v>202</v>
       </c>
-      <c r="H24" t="s" s="16">
+      <c r="J24" t="s" s="16">
         <v>203</v>
       </c>
-      <c r="I24" t="s" s="16">
+      <c r="K24" t="s" s="16">
         <v>204</v>
       </c>
-      <c r="J24" t="s" s="16">
+      <c r="L24" t="s" s="16">
         <v>205</v>
       </c>
-      <c r="K24" t="s" s="16">
+      <c r="M24" t="s" s="16">
         <v>206</v>
       </c>
-      <c r="L24" t="s" s="16">
+      <c r="N24" t="s" s="16">
         <v>207</v>
       </c>
-      <c r="M24" t="s" s="16">
+      <c r="O24" t="s" s="16">
         <v>208</v>
       </c>
-      <c r="N24" t="s" s="16">
+      <c r="P24" t="s" s="16">
         <v>209</v>
       </c>
-      <c r="O24" t="s" s="16">
+      <c r="Q24" t="s" s="16">
         <v>210</v>
       </c>
-      <c r="P24" t="s" s="16">
+      <c r="R24" t="s" s="16">
         <v>211</v>
       </c>
-      <c r="Q24" t="s" s="16">
+      <c r="S24" t="s" s="16">
         <v>212</v>
       </c>
-      <c r="R24" t="s" s="16">
+      <c r="T24" t="s" s="16">
         <v>213</v>
       </c>
-      <c r="S24" t="s" s="16">
+      <c r="U24" t="s" s="16">
         <v>214</v>
       </c>
-      <c r="T24" t="s" s="16">
+      <c r="V24" t="s" s="16">
         <v>215</v>
       </c>
-      <c r="U24" t="s" s="16">
+      <c r="W24" t="s" s="16">
         <v>216</v>
       </c>
-      <c r="V24" t="s" s="16">
+      <c r="X24" t="s" s="16">
         <v>217</v>
       </c>
-      <c r="W24" t="s" s="16">
+      <c r="Y24" t="s" s="16">
         <v>218</v>
       </c>
-      <c r="X24" t="s" s="16">
+      <c r="Z24" t="s" s="16">
         <v>219</v>
       </c>
-      <c r="Y24" t="s" s="16">
+      <c r="AA24" t="s" s="16">
         <v>220</v>
       </c>
-      <c r="Z24" t="s" s="16">
+      <c r="AB24" t="s" s="16">
         <v>221</v>
       </c>
-      <c r="AA24" t="s" s="16">
+      <c r="AC24" t="s" s="16">
         <v>222</v>
       </c>
-      <c r="AB24" t="s" s="16">
+      <c r="AD24" t="s" s="16">
         <v>223</v>
       </c>
-      <c r="AC24" t="s" s="16">
+      <c r="AE24" t="s" s="16">
         <v>224</v>
       </c>
-      <c r="AD24" t="s" s="16">
+      <c r="AF24" t="s" s="16">
         <v>225</v>
       </c>
-      <c r="AE24" t="s" s="16">
-        <v>226</v>
-      </c>
-      <c r="AF24" t="s" s="16">
-        <v>227</v>
-      </c>
       <c r="AG24" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" t="s" s="16">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s" s="16">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D25" s="17">
         <v>6</v>
       </c>
       <c r="E25" t="s" s="16">
+        <v>227</v>
+      </c>
+      <c r="F25" t="s" s="16">
+        <v>228</v>
+      </c>
+      <c r="G25" t="s" s="16">
         <v>229</v>
       </c>
-      <c r="F25" t="s" s="16">
+      <c r="H25" t="s" s="16">
         <v>230</v>
       </c>
-      <c r="G25" t="s" s="16">
+      <c r="I25" t="s" s="16">
         <v>231</v>
       </c>
-      <c r="H25" t="s" s="16">
-        <v>232</v>
-      </c>
-      <c r="I25" t="s" s="16">
-        <v>233</v>
-      </c>
       <c r="J25" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
@@ -7379,34 +7270,34 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" t="s" s="16">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s" s="16">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D26" s="17">
         <v>6</v>
       </c>
       <c r="E26" t="s" s="16">
+        <v>233</v>
+      </c>
+      <c r="F26" t="s" s="16">
+        <v>234</v>
+      </c>
+      <c r="G26" t="s" s="16">
+        <v>190</v>
+      </c>
+      <c r="H26" t="s" s="16">
         <v>235</v>
       </c>
-      <c r="F26" t="s" s="16">
+      <c r="I26" t="s" s="16">
         <v>236</v>
       </c>
-      <c r="G26" t="s" s="16">
-        <v>192</v>
-      </c>
-      <c r="H26" t="s" s="16">
-        <v>237</v>
-      </c>
-      <c r="I26" t="s" s="16">
-        <v>238</v>
-      </c>
       <c r="J26" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
@@ -7434,31 +7325,31 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" t="s" s="16">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s" s="16">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D27" s="17">
         <v>5</v>
       </c>
       <c r="E27" t="s" s="16">
+        <v>238</v>
+      </c>
+      <c r="F27" t="s" s="16">
+        <v>239</v>
+      </c>
+      <c r="G27" t="s" s="16">
         <v>240</v>
       </c>
-      <c r="F27" t="s" s="16">
+      <c r="H27" t="s" s="16">
         <v>241</v>
       </c>
-      <c r="G27" t="s" s="16">
-        <v>242</v>
-      </c>
-      <c r="H27" t="s" s="16">
-        <v>243</v>
-      </c>
       <c r="I27" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
@@ -7487,31 +7378,31 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" t="s" s="16">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s" s="16">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D28" s="17">
         <v>5</v>
       </c>
       <c r="E28" t="s" s="16">
+        <v>238</v>
+      </c>
+      <c r="F28" t="s" s="16">
+        <v>239</v>
+      </c>
+      <c r="G28" t="s" s="16">
         <v>240</v>
       </c>
-      <c r="F28" t="s" s="16">
+      <c r="H28" t="s" s="16">
         <v>241</v>
       </c>
-      <c r="G28" t="s" s="16">
-        <v>242</v>
-      </c>
-      <c r="H28" t="s" s="16">
-        <v>243</v>
-      </c>
       <c r="I28" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -7540,31 +7431,31 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" t="s" s="16">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s" s="16">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D29" s="17">
         <v>5</v>
       </c>
       <c r="E29" t="s" s="16">
+        <v>244</v>
+      </c>
+      <c r="F29" t="s" s="16">
+        <v>245</v>
+      </c>
+      <c r="G29" t="s" s="16">
         <v>246</v>
       </c>
-      <c r="F29" t="s" s="16">
+      <c r="H29" t="s" s="16">
         <v>247</v>
       </c>
-      <c r="G29" t="s" s="16">
-        <v>248</v>
-      </c>
-      <c r="H29" t="s" s="16">
-        <v>249</v>
-      </c>
       <c r="I29" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J29" s="18"/>
       <c r="K29" s="18"/>
@@ -7593,22 +7484,22 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" t="s" s="16">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D30" s="17">
         <v>2</v>
       </c>
       <c r="E30" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F30" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
@@ -7640,22 +7531,22 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" t="s" s="16">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B31" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D31" s="17">
         <v>2</v>
       </c>
       <c r="E31" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F31" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
@@ -7687,37 +7578,37 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" t="s" s="16">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s" s="16">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D32" s="17">
         <v>7</v>
       </c>
       <c r="E32" t="s" s="16">
+        <v>238</v>
+      </c>
+      <c r="F32" t="s" s="16">
+        <v>252</v>
+      </c>
+      <c r="G32" t="s" s="16">
+        <v>253</v>
+      </c>
+      <c r="H32" t="s" s="16">
         <v>240</v>
       </c>
-      <c r="F32" t="s" s="16">
+      <c r="I32" t="s" s="16">
         <v>254</v>
       </c>
-      <c r="G32" t="s" s="16">
+      <c r="J32" t="s" s="16">
         <v>255</v>
       </c>
-      <c r="H32" t="s" s="16">
-        <v>242</v>
-      </c>
-      <c r="I32" t="s" s="16">
-        <v>256</v>
-      </c>
-      <c r="J32" t="s" s="16">
-        <v>257</v>
-      </c>
       <c r="K32" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
@@ -7744,31 +7635,31 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" t="s" s="16">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B33" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s" s="16">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D33" s="17">
         <v>5</v>
       </c>
       <c r="E33" t="s" s="16">
+        <v>258</v>
+      </c>
+      <c r="F33" t="s" s="16">
+        <v>259</v>
+      </c>
+      <c r="G33" t="s" s="16">
         <v>260</v>
       </c>
-      <c r="F33" t="s" s="16">
+      <c r="H33" t="s" s="16">
         <v>261</v>
       </c>
-      <c r="G33" t="s" s="16">
-        <v>262</v>
-      </c>
-      <c r="H33" t="s" s="16">
-        <v>263</v>
-      </c>
       <c r="I33" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J33" s="18"/>
       <c r="K33" s="18"/>
@@ -7797,37 +7688,37 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" t="s" s="16">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s" s="16">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D34" s="17">
         <v>7</v>
       </c>
       <c r="E34" t="s" s="16">
+        <v>238</v>
+      </c>
+      <c r="F34" t="s" s="16">
+        <v>252</v>
+      </c>
+      <c r="G34" t="s" s="16">
+        <v>253</v>
+      </c>
+      <c r="H34" t="s" s="16">
         <v>240</v>
       </c>
-      <c r="F34" t="s" s="16">
+      <c r="I34" t="s" s="16">
         <v>254</v>
       </c>
-      <c r="G34" t="s" s="16">
+      <c r="J34" t="s" s="16">
         <v>255</v>
       </c>
-      <c r="H34" t="s" s="16">
-        <v>242</v>
-      </c>
-      <c r="I34" t="s" s="16">
-        <v>256</v>
-      </c>
-      <c r="J34" t="s" s="16">
-        <v>257</v>
-      </c>
       <c r="K34" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
@@ -7854,28 +7745,28 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" t="s" s="16">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s" s="16">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D35" s="17">
         <v>4</v>
       </c>
       <c r="E35" t="s" s="16">
+        <v>265</v>
+      </c>
+      <c r="F35" t="s" s="16">
+        <v>266</v>
+      </c>
+      <c r="G35" t="s" s="16">
         <v>267</v>
       </c>
-      <c r="F35" t="s" s="16">
-        <v>268</v>
-      </c>
-      <c r="G35" t="s" s="16">
-        <v>269</v>
-      </c>
       <c r="H35" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
@@ -7905,22 +7796,22 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" t="s" s="16">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s" s="16">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s" s="16">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D36" s="17">
         <v>2</v>
       </c>
       <c r="E36" t="s" s="16">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s" s="16">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G36" s="18"/>
       <c r="H36" s="18"/>
@@ -7952,28 +7843,28 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" t="s" s="16">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s" s="16">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D37" s="17">
         <v>4</v>
       </c>
       <c r="E37" t="s" s="16">
+        <v>270</v>
+      </c>
+      <c r="F37" t="s" s="16">
+        <v>271</v>
+      </c>
+      <c r="G37" t="s" s="16">
         <v>272</v>
       </c>
-      <c r="F37" t="s" s="16">
-        <v>273</v>
-      </c>
-      <c r="G37" t="s" s="16">
-        <v>274</v>
-      </c>
       <c r="H37" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
@@ -8003,64 +7894,64 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" t="s" s="16">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s" s="16">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D38" s="17">
         <v>16</v>
       </c>
       <c r="E38" t="s" s="16">
+        <v>274</v>
+      </c>
+      <c r="F38" t="s" s="16">
+        <v>275</v>
+      </c>
+      <c r="G38" t="s" s="16">
         <v>276</v>
       </c>
-      <c r="F38" t="s" s="16">
+      <c r="H38" t="s" s="16">
         <v>277</v>
       </c>
-      <c r="G38" t="s" s="16">
+      <c r="I38" t="s" s="16">
         <v>278</v>
       </c>
-      <c r="H38" t="s" s="16">
+      <c r="J38" t="s" s="16">
         <v>279</v>
       </c>
-      <c r="I38" t="s" s="16">
+      <c r="K38" t="s" s="16">
         <v>280</v>
       </c>
-      <c r="J38" t="s" s="16">
+      <c r="L38" t="s" s="16">
         <v>281</v>
       </c>
-      <c r="K38" t="s" s="16">
+      <c r="M38" t="s" s="16">
         <v>282</v>
       </c>
-      <c r="L38" t="s" s="16">
+      <c r="N38" t="s" s="16">
         <v>283</v>
       </c>
-      <c r="M38" t="s" s="16">
+      <c r="O38" t="s" s="16">
         <v>284</v>
       </c>
-      <c r="N38" t="s" s="16">
+      <c r="P38" t="s" s="16">
         <v>285</v>
       </c>
-      <c r="O38" t="s" s="16">
+      <c r="Q38" t="s" s="16">
         <v>286</v>
       </c>
-      <c r="P38" t="s" s="16">
+      <c r="R38" t="s" s="16">
         <v>287</v>
       </c>
-      <c r="Q38" t="s" s="16">
+      <c r="S38" t="s" s="16">
         <v>288</v>
       </c>
-      <c r="R38" t="s" s="16">
-        <v>289</v>
-      </c>
-      <c r="S38" t="s" s="16">
-        <v>290</v>
-      </c>
       <c r="T38" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="U38" s="18"/>
       <c r="V38" s="18"/>
@@ -8078,25 +7969,25 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" t="s" s="16">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s" s="16">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D39" s="17">
         <v>3</v>
       </c>
       <c r="E39" t="s" s="16">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F39" t="s" s="16">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G39" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
@@ -8127,28 +8018,28 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" t="s" s="16">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B40" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s" s="16">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D40" s="17">
         <v>4</v>
       </c>
       <c r="E40" t="s" s="16">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F40" t="s" s="16">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G40" t="s" s="16">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H40" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I40" s="18"/>
       <c r="J40" s="18"/>
@@ -8178,28 +8069,28 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" t="s" s="16">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B41" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s" s="16">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D41" s="17">
         <v>4</v>
       </c>
       <c r="E41" t="s" s="16">
+        <v>299</v>
+      </c>
+      <c r="F41" t="s" s="16">
+        <v>300</v>
+      </c>
+      <c r="G41" t="s" s="16">
         <v>301</v>
       </c>
-      <c r="F41" t="s" s="16">
-        <v>302</v>
-      </c>
-      <c r="G41" t="s" s="16">
-        <v>303</v>
-      </c>
       <c r="H41" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
@@ -8229,25 +8120,25 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" t="s" s="16">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B42" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s" s="16">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D42" s="17">
         <v>3</v>
       </c>
       <c r="E42" t="s" s="16">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F42" t="s" s="16">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G42" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H42" s="18"/>
       <c r="I42" s="18"/>
@@ -8278,25 +8169,25 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" t="s" s="16">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s" s="16">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D43" s="17">
         <v>3</v>
       </c>
       <c r="E43" t="s" s="16">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F43" t="s" s="16">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G43" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H43" s="18"/>
       <c r="I43" s="18"/>
@@ -8327,31 +8218,31 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" t="s" s="16">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s" s="16">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D44" s="17">
         <v>5</v>
       </c>
       <c r="E44" t="s" s="16">
+        <v>311</v>
+      </c>
+      <c r="F44" t="s" s="16">
+        <v>312</v>
+      </c>
+      <c r="G44" t="s" s="16">
         <v>313</v>
       </c>
-      <c r="F44" t="s" s="16">
+      <c r="H44" t="s" s="16">
         <v>314</v>
       </c>
-      <c r="G44" t="s" s="16">
-        <v>315</v>
-      </c>
-      <c r="H44" t="s" s="16">
-        <v>316</v>
-      </c>
       <c r="I44" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
@@ -8380,40 +8271,40 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" t="s" s="16">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B45" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s" s="16">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D45" s="17">
         <v>8</v>
       </c>
       <c r="E45" t="s" s="16">
+        <v>317</v>
+      </c>
+      <c r="F45" t="s" s="16">
+        <v>318</v>
+      </c>
+      <c r="G45" t="s" s="16">
         <v>319</v>
       </c>
-      <c r="F45" t="s" s="16">
+      <c r="H45" t="s" s="16">
         <v>320</v>
       </c>
-      <c r="G45" t="s" s="16">
+      <c r="I45" t="s" s="16">
         <v>321</v>
       </c>
-      <c r="H45" t="s" s="16">
+      <c r="J45" t="s" s="16">
         <v>322</v>
       </c>
-      <c r="I45" t="s" s="16">
+      <c r="K45" t="s" s="16">
         <v>323</v>
       </c>
-      <c r="J45" t="s" s="16">
-        <v>324</v>
-      </c>
-      <c r="K45" t="s" s="16">
-        <v>325</v>
-      </c>
       <c r="L45" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M45" s="18"/>
       <c r="N45" s="18"/>
@@ -8439,28 +8330,28 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" t="s" s="16">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s" s="16">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D46" s="17">
         <v>4</v>
       </c>
       <c r="E46" t="s" s="16">
+        <v>138</v>
+      </c>
+      <c r="F46" t="s" s="16">
+        <v>139</v>
+      </c>
+      <c r="G46" t="s" s="16">
         <v>140</v>
       </c>
-      <c r="F46" t="s" s="16">
-        <v>141</v>
-      </c>
-      <c r="G46" t="s" s="16">
-        <v>142</v>
-      </c>
       <c r="H46" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
@@ -8490,28 +8381,28 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" t="s" s="16">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s" s="16">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D47" s="17">
         <v>4</v>
       </c>
       <c r="E47" t="s" s="16">
+        <v>328</v>
+      </c>
+      <c r="F47" t="s" s="16">
+        <v>329</v>
+      </c>
+      <c r="G47" t="s" s="16">
         <v>330</v>
       </c>
-      <c r="F47" t="s" s="16">
-        <v>331</v>
-      </c>
-      <c r="G47" t="s" s="16">
-        <v>332</v>
-      </c>
       <c r="H47" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I47" s="18"/>
       <c r="J47" s="18"/>
@@ -8541,28 +8432,28 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" t="s" s="16">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s" s="16">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D48" s="17">
         <v>4</v>
       </c>
       <c r="E48" t="s" s="16">
+        <v>328</v>
+      </c>
+      <c r="F48" t="s" s="16">
+        <v>329</v>
+      </c>
+      <c r="G48" t="s" s="16">
         <v>330</v>
       </c>
-      <c r="F48" t="s" s="16">
-        <v>331</v>
-      </c>
-      <c r="G48" t="s" s="16">
-        <v>332</v>
-      </c>
       <c r="H48" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
@@ -8592,55 +8483,55 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" t="s" s="16">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D49" s="17">
         <v>13</v>
       </c>
       <c r="E49" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F49" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G49" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F49" t="s" s="16">
+      <c r="H49" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G49" t="s" s="16">
+      <c r="I49" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H49" t="s" s="16">
+      <c r="J49" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I49" t="s" s="16">
+      <c r="K49" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J49" t="s" s="16">
+      <c r="L49" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K49" t="s" s="16">
+      <c r="M49" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L49" t="s" s="16">
+      <c r="N49" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M49" t="s" s="16">
+      <c r="O49" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N49" t="s" s="16">
+      <c r="P49" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O49" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P49" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q49" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R49" s="18"/>
       <c r="S49" s="18"/>
@@ -8661,55 +8552,55 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" t="s" s="16">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B50" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D50" s="17">
         <v>13</v>
       </c>
       <c r="E50" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F50" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G50" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F50" t="s" s="16">
+      <c r="H50" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G50" t="s" s="16">
+      <c r="I50" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H50" t="s" s="16">
+      <c r="J50" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I50" t="s" s="16">
+      <c r="K50" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J50" t="s" s="16">
+      <c r="L50" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K50" t="s" s="16">
+      <c r="M50" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L50" t="s" s="16">
+      <c r="N50" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M50" t="s" s="16">
+      <c r="O50" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N50" t="s" s="16">
+      <c r="P50" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O50" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P50" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q50" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R50" s="18"/>
       <c r="S50" s="18"/>
@@ -8730,55 +8621,55 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" t="s" s="16">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D51" s="17">
         <v>13</v>
       </c>
       <c r="E51" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F51" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G51" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F51" t="s" s="16">
+      <c r="H51" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G51" t="s" s="16">
+      <c r="I51" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H51" t="s" s="16">
+      <c r="J51" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I51" t="s" s="16">
+      <c r="K51" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J51" t="s" s="16">
+      <c r="L51" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K51" t="s" s="16">
+      <c r="M51" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L51" t="s" s="16">
+      <c r="N51" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M51" t="s" s="16">
+      <c r="O51" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N51" t="s" s="16">
+      <c r="P51" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O51" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P51" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q51" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R51" s="18"/>
       <c r="S51" s="18"/>
@@ -8799,55 +8690,55 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" t="s" s="16">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B52" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D52" s="17">
         <v>13</v>
       </c>
       <c r="E52" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F52" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G52" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F52" t="s" s="16">
+      <c r="H52" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G52" t="s" s="16">
+      <c r="I52" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H52" t="s" s="16">
+      <c r="J52" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I52" t="s" s="16">
+      <c r="K52" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J52" t="s" s="16">
+      <c r="L52" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K52" t="s" s="16">
+      <c r="M52" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L52" t="s" s="16">
+      <c r="N52" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M52" t="s" s="16">
+      <c r="O52" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N52" t="s" s="16">
+      <c r="P52" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O52" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P52" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q52" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R52" s="18"/>
       <c r="S52" s="18"/>
@@ -8868,61 +8759,61 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" t="s" s="16">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B53" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s" s="16">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D53" s="17">
         <v>15</v>
       </c>
       <c r="E53" t="s" s="16">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F53" t="s" s="16">
+        <v>342</v>
+      </c>
+      <c r="G53" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="H53" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="I53" t="s" s="16">
+        <v>336</v>
+      </c>
+      <c r="J53" t="s" s="16">
+        <v>337</v>
+      </c>
+      <c r="K53" t="s" s="16">
+        <v>338</v>
+      </c>
+      <c r="L53" t="s" s="16">
+        <v>339</v>
+      </c>
+      <c r="M53" t="s" s="16">
+        <v>340</v>
+      </c>
+      <c r="N53" t="s" s="16">
+        <v>341</v>
+      </c>
+      <c r="O53" t="s" s="16">
+        <v>342</v>
+      </c>
+      <c r="P53" t="s" s="16">
+        <v>351</v>
+      </c>
+      <c r="Q53" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="G53" t="s" s="16">
-        <v>336</v>
-      </c>
-      <c r="H53" t="s" s="16">
-        <v>337</v>
-      </c>
-      <c r="I53" t="s" s="16">
-        <v>338</v>
-      </c>
-      <c r="J53" t="s" s="16">
-        <v>339</v>
-      </c>
-      <c r="K53" t="s" s="16">
-        <v>340</v>
-      </c>
-      <c r="L53" t="s" s="16">
-        <v>341</v>
-      </c>
-      <c r="M53" t="s" s="16">
-        <v>342</v>
-      </c>
-      <c r="N53" t="s" s="16">
-        <v>343</v>
-      </c>
-      <c r="O53" t="s" s="16">
-        <v>344</v>
-      </c>
-      <c r="P53" t="s" s="16">
-        <v>353</v>
-      </c>
-      <c r="Q53" t="s" s="16">
-        <v>346</v>
-      </c>
       <c r="R53" t="s" s="16">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="S53" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T53" s="18"/>
       <c r="U53" s="18"/>
@@ -8941,55 +8832,55 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" t="s" s="16">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D54" s="17">
         <v>13</v>
       </c>
       <c r="E54" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F54" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G54" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F54" t="s" s="16">
+      <c r="H54" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G54" t="s" s="16">
+      <c r="I54" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H54" t="s" s="16">
+      <c r="J54" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I54" t="s" s="16">
+      <c r="K54" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J54" t="s" s="16">
+      <c r="L54" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K54" t="s" s="16">
+      <c r="M54" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L54" t="s" s="16">
+      <c r="N54" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M54" t="s" s="16">
+      <c r="O54" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N54" t="s" s="16">
+      <c r="P54" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O54" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P54" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q54" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R54" s="18"/>
       <c r="S54" s="18"/>
@@ -9010,55 +8901,55 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" t="s" s="16">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C55" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D55" s="17">
         <v>13</v>
       </c>
       <c r="E55" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F55" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G55" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F55" t="s" s="16">
+      <c r="H55" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G55" t="s" s="16">
+      <c r="I55" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H55" t="s" s="16">
+      <c r="J55" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I55" t="s" s="16">
+      <c r="K55" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J55" t="s" s="16">
+      <c r="L55" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K55" t="s" s="16">
+      <c r="M55" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L55" t="s" s="16">
+      <c r="N55" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M55" t="s" s="16">
+      <c r="O55" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N55" t="s" s="16">
+      <c r="P55" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O55" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P55" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q55" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R55" s="18"/>
       <c r="S55" s="18"/>
@@ -9079,55 +8970,55 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" t="s" s="16">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D56" s="17">
         <v>13</v>
       </c>
       <c r="E56" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F56" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G56" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F56" t="s" s="16">
+      <c r="H56" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G56" t="s" s="16">
+      <c r="I56" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H56" t="s" s="16">
+      <c r="J56" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I56" t="s" s="16">
+      <c r="K56" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J56" t="s" s="16">
+      <c r="L56" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K56" t="s" s="16">
+      <c r="M56" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L56" t="s" s="16">
+      <c r="N56" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M56" t="s" s="16">
+      <c r="O56" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N56" t="s" s="16">
+      <c r="P56" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O56" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P56" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q56" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R56" s="18"/>
       <c r="S56" s="18"/>
@@ -9148,55 +9039,55 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" t="s" s="16">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D57" s="17">
         <v>13</v>
       </c>
       <c r="E57" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F57" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G57" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F57" t="s" s="16">
+      <c r="H57" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G57" t="s" s="16">
+      <c r="I57" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H57" t="s" s="16">
+      <c r="J57" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I57" t="s" s="16">
+      <c r="K57" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J57" t="s" s="16">
+      <c r="L57" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K57" t="s" s="16">
+      <c r="M57" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L57" t="s" s="16">
+      <c r="N57" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M57" t="s" s="16">
+      <c r="O57" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N57" t="s" s="16">
+      <c r="P57" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O57" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P57" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q57" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R57" s="18"/>
       <c r="S57" s="18"/>
@@ -9217,55 +9108,55 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" t="s" s="16">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B58" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D58" s="17">
         <v>13</v>
       </c>
       <c r="E58" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F58" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G58" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F58" t="s" s="16">
+      <c r="H58" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G58" t="s" s="16">
+      <c r="I58" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H58" t="s" s="16">
+      <c r="J58" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I58" t="s" s="16">
+      <c r="K58" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J58" t="s" s="16">
+      <c r="L58" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K58" t="s" s="16">
+      <c r="M58" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L58" t="s" s="16">
+      <c r="N58" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M58" t="s" s="16">
+      <c r="O58" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N58" t="s" s="16">
+      <c r="P58" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O58" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P58" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q58" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R58" s="18"/>
       <c r="S58" s="18"/>
@@ -9286,55 +9177,55 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" t="s" s="16">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B59" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C59" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D59" s="17">
         <v>13</v>
       </c>
       <c r="E59" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F59" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G59" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F59" t="s" s="16">
+      <c r="H59" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G59" t="s" s="16">
+      <c r="I59" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H59" t="s" s="16">
+      <c r="J59" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I59" t="s" s="16">
+      <c r="K59" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J59" t="s" s="16">
+      <c r="L59" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K59" t="s" s="16">
+      <c r="M59" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L59" t="s" s="16">
+      <c r="N59" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M59" t="s" s="16">
+      <c r="O59" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N59" t="s" s="16">
+      <c r="P59" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O59" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P59" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q59" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R59" s="18"/>
       <c r="S59" s="18"/>
@@ -9355,55 +9246,55 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" t="s" s="16">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B60" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C60" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D60" s="17">
         <v>13</v>
       </c>
       <c r="E60" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F60" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G60" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F60" t="s" s="16">
+      <c r="H60" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G60" t="s" s="16">
+      <c r="I60" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H60" t="s" s="16">
+      <c r="J60" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I60" t="s" s="16">
+      <c r="K60" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J60" t="s" s="16">
+      <c r="L60" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K60" t="s" s="16">
+      <c r="M60" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L60" t="s" s="16">
+      <c r="N60" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M60" t="s" s="16">
+      <c r="O60" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N60" t="s" s="16">
+      <c r="P60" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O60" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P60" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q60" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R60" s="18"/>
       <c r="S60" s="18"/>
@@ -9424,55 +9315,55 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" t="s" s="16">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B61" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D61" s="17">
         <v>13</v>
       </c>
       <c r="E61" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F61" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G61" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F61" t="s" s="16">
+      <c r="H61" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G61" t="s" s="16">
+      <c r="I61" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H61" t="s" s="16">
+      <c r="J61" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I61" t="s" s="16">
+      <c r="K61" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J61" t="s" s="16">
+      <c r="L61" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K61" t="s" s="16">
+      <c r="M61" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L61" t="s" s="16">
+      <c r="N61" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M61" t="s" s="16">
+      <c r="O61" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N61" t="s" s="16">
+      <c r="P61" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O61" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P61" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q61" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R61" s="18"/>
       <c r="S61" s="18"/>
@@ -9493,55 +9384,55 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" t="s" s="16">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B62" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C62" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D62" s="17">
         <v>13</v>
       </c>
       <c r="E62" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F62" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G62" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F62" t="s" s="16">
+      <c r="H62" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G62" t="s" s="16">
+      <c r="I62" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H62" t="s" s="16">
+      <c r="J62" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I62" t="s" s="16">
+      <c r="K62" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J62" t="s" s="16">
+      <c r="L62" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K62" t="s" s="16">
+      <c r="M62" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L62" t="s" s="16">
+      <c r="N62" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M62" t="s" s="16">
+      <c r="O62" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N62" t="s" s="16">
+      <c r="P62" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O62" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P62" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q62" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R62" s="18"/>
       <c r="S62" s="18"/>
@@ -9562,55 +9453,55 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" t="s" s="16">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B63" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C63" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D63" s="17">
         <v>13</v>
       </c>
       <c r="E63" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F63" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G63" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F63" t="s" s="16">
+      <c r="H63" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G63" t="s" s="16">
+      <c r="I63" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H63" t="s" s="16">
+      <c r="J63" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I63" t="s" s="16">
+      <c r="K63" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J63" t="s" s="16">
+      <c r="L63" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K63" t="s" s="16">
+      <c r="M63" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L63" t="s" s="16">
+      <c r="N63" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M63" t="s" s="16">
+      <c r="O63" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N63" t="s" s="16">
+      <c r="P63" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O63" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P63" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q63" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R63" s="18"/>
       <c r="S63" s="18"/>
@@ -9631,55 +9522,55 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" t="s" s="16">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B64" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C64" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D64" s="17">
         <v>13</v>
       </c>
       <c r="E64" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F64" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G64" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F64" t="s" s="16">
+      <c r="H64" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G64" t="s" s="16">
+      <c r="I64" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H64" t="s" s="16">
+      <c r="J64" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I64" t="s" s="16">
+      <c r="K64" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J64" t="s" s="16">
+      <c r="L64" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K64" t="s" s="16">
+      <c r="M64" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L64" t="s" s="16">
+      <c r="N64" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M64" t="s" s="16">
+      <c r="O64" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N64" t="s" s="16">
+      <c r="P64" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O64" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P64" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q64" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R64" s="18"/>
       <c r="S64" s="18"/>
@@ -9700,55 +9591,55 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" t="s" s="16">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D65" s="17">
         <v>13</v>
       </c>
       <c r="E65" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F65" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G65" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F65" t="s" s="16">
+      <c r="H65" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G65" t="s" s="16">
+      <c r="I65" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H65" t="s" s="16">
+      <c r="J65" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I65" t="s" s="16">
+      <c r="K65" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J65" t="s" s="16">
+      <c r="L65" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K65" t="s" s="16">
+      <c r="M65" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L65" t="s" s="16">
+      <c r="N65" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M65" t="s" s="16">
+      <c r="O65" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N65" t="s" s="16">
+      <c r="P65" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O65" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P65" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q65" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R65" s="18"/>
       <c r="S65" s="18"/>
@@ -9769,55 +9660,55 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" t="s" s="16">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D66" s="17">
         <v>13</v>
       </c>
       <c r="E66" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F66" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G66" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F66" t="s" s="16">
+      <c r="H66" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G66" t="s" s="16">
+      <c r="I66" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H66" t="s" s="16">
+      <c r="J66" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I66" t="s" s="16">
+      <c r="K66" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J66" t="s" s="16">
+      <c r="L66" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K66" t="s" s="16">
+      <c r="M66" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L66" t="s" s="16">
+      <c r="N66" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M66" t="s" s="16">
+      <c r="O66" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N66" t="s" s="16">
+      <c r="P66" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O66" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P66" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q66" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R66" s="18"/>
       <c r="S66" s="18"/>
@@ -9838,55 +9729,55 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" t="s" s="16">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B67" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D67" s="17">
         <v>13</v>
       </c>
       <c r="E67" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F67" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G67" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F67" t="s" s="16">
+      <c r="H67" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G67" t="s" s="16">
+      <c r="I67" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H67" t="s" s="16">
+      <c r="J67" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I67" t="s" s="16">
+      <c r="K67" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J67" t="s" s="16">
+      <c r="L67" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K67" t="s" s="16">
+      <c r="M67" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L67" t="s" s="16">
+      <c r="N67" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M67" t="s" s="16">
+      <c r="O67" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N67" t="s" s="16">
+      <c r="P67" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O67" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P67" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q67" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R67" s="18"/>
       <c r="S67" s="18"/>
@@ -9907,55 +9798,55 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" t="s" s="16">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B68" t="s" s="16">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C68" t="s" s="16">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D68" s="17">
         <v>13</v>
       </c>
       <c r="E68" t="s" s="16">
+        <v>334</v>
+      </c>
+      <c r="F68" t="s" s="16">
+        <v>335</v>
+      </c>
+      <c r="G68" t="s" s="16">
         <v>336</v>
       </c>
-      <c r="F68" t="s" s="16">
+      <c r="H68" t="s" s="16">
         <v>337</v>
       </c>
-      <c r="G68" t="s" s="16">
+      <c r="I68" t="s" s="16">
         <v>338</v>
       </c>
-      <c r="H68" t="s" s="16">
+      <c r="J68" t="s" s="16">
         <v>339</v>
       </c>
-      <c r="I68" t="s" s="16">
+      <c r="K68" t="s" s="16">
         <v>340</v>
       </c>
-      <c r="J68" t="s" s="16">
+      <c r="L68" t="s" s="16">
         <v>341</v>
       </c>
-      <c r="K68" t="s" s="16">
+      <c r="M68" t="s" s="16">
         <v>342</v>
       </c>
-      <c r="L68" t="s" s="16">
+      <c r="N68" t="s" s="16">
         <v>343</v>
       </c>
-      <c r="M68" t="s" s="16">
+      <c r="O68" t="s" s="16">
         <v>344</v>
       </c>
-      <c r="N68" t="s" s="16">
+      <c r="P68" t="s" s="16">
         <v>345</v>
       </c>
-      <c r="O68" t="s" s="16">
-        <v>346</v>
-      </c>
-      <c r="P68" t="s" s="16">
-        <v>347</v>
-      </c>
       <c r="Q68" t="s" s="16">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R68" s="18"/>
       <c r="S68" s="18"/>
@@ -10009,314 +9900,314 @@
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="20">
+        <v>367</v>
+      </c>
+      <c r="B1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s" s="22">
+        <v>368</v>
+      </c>
+      <c r="F1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s" s="21">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s" s="23">
         <v>369</v>
       </c>
-      <c r="B1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="E1" t="s" s="22">
-        <v>370</v>
-      </c>
-      <c r="F1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="I1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="L1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s" s="23">
-        <v>371</v>
-      </c>
       <c r="N1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AB1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF1" t="s" s="23">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG1" t="s" s="23">
-        <v>371</v>
-      </c>
-      <c r="AH1" t="s" s="22">
-        <v>370</v>
+        <v>369</v>
+      </c>
+      <c r="AH1" t="s" s="25">
+        <v>368</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>371</v>
+      </c>
+      <c r="C2" t="s" s="26">
+        <v>371</v>
+      </c>
+      <c r="D2" t="s" s="26">
+        <v>371</v>
+      </c>
+      <c r="E2" t="s" s="26">
         <v>372</v>
       </c>
-      <c r="B2" t="s" s="25">
+      <c r="F2" t="s" s="26">
         <v>373</v>
       </c>
-      <c r="C2" t="s" s="25">
+      <c r="G2" t="s" s="26">
         <v>373</v>
       </c>
-      <c r="D2" t="s" s="25">
+      <c r="H2" t="s" s="26">
         <v>373</v>
       </c>
-      <c r="E2" t="s" s="25">
+      <c r="I2" t="s" s="26">
+        <v>373</v>
+      </c>
+      <c r="J2" t="s" s="26">
+        <v>373</v>
+      </c>
+      <c r="K2" t="s" s="26">
+        <v>373</v>
+      </c>
+      <c r="L2" t="s" s="26">
+        <v>373</v>
+      </c>
+      <c r="M2" t="s" s="26">
+        <v>373</v>
+      </c>
+      <c r="N2" t="s" s="26">
+        <v>373</v>
+      </c>
+      <c r="O2" t="s" s="26">
+        <v>373</v>
+      </c>
+      <c r="P2" t="s" s="26">
         <v>374</v>
       </c>
-      <c r="F2" t="s" s="25">
+      <c r="Q2" t="s" s="26">
+        <v>374</v>
+      </c>
+      <c r="R2" t="s" s="26">
+        <v>374</v>
+      </c>
+      <c r="S2" t="s" s="26">
         <v>375</v>
       </c>
-      <c r="G2" t="s" s="25">
+      <c r="T2" t="s" s="26">
         <v>375</v>
       </c>
-      <c r="H2" t="s" s="25">
+      <c r="U2" t="s" s="26">
         <v>375</v>
       </c>
-      <c r="I2" t="s" s="25">
+      <c r="V2" t="s" s="26">
         <v>375</v>
       </c>
-      <c r="J2" t="s" s="25">
+      <c r="W2" t="s" s="26">
         <v>375</v>
       </c>
-      <c r="K2" t="s" s="25">
+      <c r="X2" t="s" s="26">
         <v>375</v>
       </c>
-      <c r="L2" t="s" s="25">
+      <c r="Y2" t="s" s="26">
         <v>375</v>
       </c>
-      <c r="M2" t="s" s="25">
-        <v>375</v>
-      </c>
-      <c r="N2" t="s" s="25">
-        <v>375</v>
-      </c>
-      <c r="O2" t="s" s="25">
-        <v>375</v>
-      </c>
-      <c r="P2" t="s" s="25">
+      <c r="Z2" t="s" s="26">
         <v>376</v>
       </c>
-      <c r="Q2" t="s" s="25">
+      <c r="AA2" t="s" s="26">
         <v>376</v>
       </c>
-      <c r="R2" t="s" s="25">
+      <c r="AB2" t="s" s="26">
         <v>376</v>
       </c>
-      <c r="S2" t="s" s="25">
+      <c r="AC2" t="s" s="26">
+        <v>376</v>
+      </c>
+      <c r="AD2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="AE2" t="s" s="26">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="s" s="26">
         <v>377</v>
       </c>
-      <c r="T2" t="s" s="25">
+      <c r="AG2" t="s" s="26">
         <v>377</v>
       </c>
-      <c r="U2" t="s" s="25">
+      <c r="AH2" t="s" s="26">
         <v>377</v>
-      </c>
-      <c r="V2" t="s" s="25">
-        <v>377</v>
-      </c>
-      <c r="W2" t="s" s="25">
-        <v>377</v>
-      </c>
-      <c r="X2" t="s" s="25">
-        <v>377</v>
-      </c>
-      <c r="Y2" t="s" s="25">
-        <v>377</v>
-      </c>
-      <c r="Z2" t="s" s="25">
-        <v>378</v>
-      </c>
-      <c r="AA2" t="s" s="25">
-        <v>378</v>
-      </c>
-      <c r="AB2" t="s" s="25">
-        <v>378</v>
-      </c>
-      <c r="AC2" t="s" s="25">
-        <v>378</v>
-      </c>
-      <c r="AD2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="AE2" t="s" s="25">
-        <v>48</v>
-      </c>
-      <c r="AF2" t="s" s="25">
-        <v>379</v>
-      </c>
-      <c r="AG2" t="s" s="25">
-        <v>379</v>
-      </c>
-      <c r="AH2" t="s" s="25">
-        <v>379</v>
       </c>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="12">
+        <v>378</v>
+      </c>
+      <c r="B3" t="s" s="12">
+        <v>106</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>112</v>
+      </c>
+      <c r="D3" t="s" s="12">
+        <v>379</v>
+      </c>
+      <c r="E3" t="s" s="12">
         <v>380</v>
       </c>
-      <c r="B3" t="s" s="12">
-        <v>108</v>
-      </c>
-      <c r="C3" t="s" s="12">
-        <v>114</v>
-      </c>
-      <c r="D3" t="s" s="12">
+      <c r="F3" t="s" s="12">
         <v>381</v>
       </c>
-      <c r="E3" t="s" s="12">
+      <c r="G3" t="s" s="12">
         <v>382</v>
       </c>
-      <c r="F3" t="s" s="12">
+      <c r="H3" t="s" s="12">
         <v>383</v>
       </c>
-      <c r="G3" t="s" s="12">
+      <c r="I3" t="s" s="12">
         <v>384</v>
       </c>
-      <c r="H3" t="s" s="12">
+      <c r="J3" t="s" s="12">
         <v>385</v>
       </c>
-      <c r="I3" t="s" s="12">
+      <c r="K3" t="s" s="12">
         <v>386</v>
       </c>
-      <c r="J3" t="s" s="12">
+      <c r="L3" t="s" s="12">
         <v>387</v>
       </c>
-      <c r="K3" t="s" s="12">
+      <c r="M3" t="s" s="12">
         <v>388</v>
       </c>
-      <c r="L3" t="s" s="12">
+      <c r="N3" t="s" s="12">
         <v>389</v>
       </c>
-      <c r="M3" t="s" s="12">
+      <c r="O3" t="s" s="12">
+        <v>134</v>
+      </c>
+      <c r="P3" t="s" s="12">
         <v>390</v>
       </c>
-      <c r="N3" t="s" s="12">
+      <c r="Q3" t="s" s="12">
+        <v>145</v>
+      </c>
+      <c r="R3" t="s" s="12">
         <v>391</v>
       </c>
-      <c r="O3" t="s" s="12">
-        <v>136</v>
-      </c>
-      <c r="P3" t="s" s="12">
+      <c r="S3" t="s" s="12">
         <v>392</v>
       </c>
-      <c r="Q3" t="s" s="12">
-        <v>147</v>
-      </c>
-      <c r="R3" t="s" s="12">
+      <c r="T3" t="s" s="12">
         <v>393</v>
       </c>
-      <c r="S3" t="s" s="12">
+      <c r="U3" t="s" s="12">
+        <v>161</v>
+      </c>
+      <c r="V3" t="s" s="12">
+        <v>170</v>
+      </c>
+      <c r="W3" t="s" s="12">
         <v>394</v>
       </c>
-      <c r="T3" t="s" s="12">
+      <c r="X3" t="s" s="12">
         <v>395</v>
       </c>
-      <c r="U3" t="s" s="12">
-        <v>163</v>
-      </c>
-      <c r="V3" t="s" s="12">
-        <v>172</v>
-      </c>
-      <c r="W3" t="s" s="12">
+      <c r="Y3" t="s" s="12">
         <v>396</v>
       </c>
-      <c r="X3" t="s" s="12">
+      <c r="Z3" t="s" s="12">
         <v>397</v>
       </c>
-      <c r="Y3" t="s" s="12">
+      <c r="AA3" t="s" s="12">
+        <v>175</v>
+      </c>
+      <c r="AB3" t="s" s="12">
         <v>398</v>
       </c>
-      <c r="Z3" t="s" s="12">
+      <c r="AC3" t="s" s="12">
         <v>399</v>
       </c>
-      <c r="AA3" t="s" s="12">
-        <v>177</v>
-      </c>
-      <c r="AB3" t="s" s="12">
+      <c r="AD3" t="s" s="12">
+        <v>26</v>
+      </c>
+      <c r="AE3" t="s" s="12">
+        <v>268</v>
+      </c>
+      <c r="AF3" t="s" s="12">
         <v>400</v>
       </c>
-      <c r="AC3" t="s" s="12">
+      <c r="AG3" t="s" s="12">
         <v>401</v>
       </c>
-      <c r="AD3" t="s" s="12">
-        <v>28</v>
-      </c>
-      <c r="AE3" t="s" s="12">
-        <v>270</v>
-      </c>
-      <c r="AF3" t="s" s="12">
+      <c r="AH3" t="s" s="12">
         <v>402</v>
-      </c>
-      <c r="AG3" t="s" s="12">
-        <v>403</v>
-      </c>
-      <c r="AH3" t="s" s="12">
-        <v>404</v>
       </c>
     </row>
     <row r="4" ht="13.55" customHeight="1">
@@ -10616,63 +10507,63 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="26" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="26" customWidth="1"/>
-    <col min="3" max="3" width="11.8516" style="26" customWidth="1"/>
-    <col min="4" max="4" width="12" style="26" customWidth="1"/>
-    <col min="5" max="5" width="22.1719" style="26" customWidth="1"/>
-    <col min="6" max="16384" width="14.5" style="26" customWidth="1"/>
+    <col min="1" max="1" width="23.5" style="27" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="27" customWidth="1"/>
+    <col min="3" max="3" width="11.8516" style="27" customWidth="1"/>
+    <col min="4" max="4" width="12" style="27" customWidth="1"/>
+    <col min="5" max="5" width="22.1719" style="27" customWidth="1"/>
+    <col min="6" max="16384" width="14.5" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="20">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="E1" t="s" s="27">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="E1" t="s" s="28">
+        <v>12</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s" s="25">
-        <v>48</v>
+        <v>370</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s" s="26">
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="12">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B3" t="s" s="12">
+        <v>403</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s" s="12">
+        <v>404</v>
+      </c>
+      <c r="E3" t="s" s="12">
         <v>405</v>
-      </c>
-      <c r="C3" t="s" s="12">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s" s="12">
-        <v>406</v>
-      </c>
-      <c r="E3" t="s" s="12">
-        <v>407</v>
       </c>
     </row>
     <row r="4" ht="13.55" customHeight="1">
@@ -10740,99 +10631,99 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="28" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="28" customWidth="1"/>
-    <col min="3" max="3" width="11.8516" style="28" customWidth="1"/>
-    <col min="4" max="4" width="12" style="28" customWidth="1"/>
-    <col min="5" max="9" width="22.1719" style="28" customWidth="1"/>
-    <col min="10" max="16384" width="14.5" style="28" customWidth="1"/>
+    <col min="1" max="1" width="23.5" style="29" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="29" customWidth="1"/>
+    <col min="3" max="3" width="11.8516" style="29" customWidth="1"/>
+    <col min="4" max="4" width="12" style="29" customWidth="1"/>
+    <col min="5" max="9" width="22.1719" style="29" customWidth="1"/>
+    <col min="10" max="16384" width="14.5" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="20">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" t="s" s="24">
-        <v>20</v>
-      </c>
-      <c r="I1" t="s" s="29">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="I1" t="s" s="30">
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s" s="25">
-        <v>48</v>
-      </c>
-      <c r="F2" t="s" s="25">
-        <v>48</v>
-      </c>
-      <c r="G2" t="s" s="25">
-        <v>48</v>
-      </c>
-      <c r="H2" t="s" s="25">
-        <v>48</v>
-      </c>
-      <c r="I2" t="s" s="25">
-        <v>48</v>
+        <v>370</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s" s="26">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s" s="26">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s" s="26">
+        <v>46</v>
+      </c>
+      <c r="H2" t="s" s="26">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s" s="26">
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="12">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B3" t="s" s="12">
+        <v>403</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s" s="12">
+        <v>404</v>
+      </c>
+      <c r="E3" t="s" s="12">
+        <v>406</v>
+      </c>
+      <c r="F3" t="s" s="12">
+        <v>250</v>
+      </c>
+      <c r="G3" t="s" s="12">
         <v>405</v>
       </c>
-      <c r="C3" t="s" s="12">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s" s="12">
-        <v>406</v>
-      </c>
-      <c r="E3" t="s" s="12">
+      <c r="H3" t="s" s="12">
+        <v>407</v>
+      </c>
+      <c r="I3" t="s" s="12">
         <v>408</v>
-      </c>
-      <c r="F3" t="s" s="12">
-        <v>252</v>
-      </c>
-      <c r="G3" t="s" s="12">
-        <v>407</v>
-      </c>
-      <c r="H3" t="s" s="12">
-        <v>409</v>
-      </c>
-      <c r="I3" t="s" s="12">
-        <v>410</v>
       </c>
     </row>
     <row r="4" ht="13.55" customHeight="1">
@@ -10933,18 +10824,18 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22.1719" style="30" customWidth="1"/>
-    <col min="3" max="5" width="14.5" style="30" customWidth="1"/>
-    <col min="6" max="16384" width="14.5" style="30" customWidth="1"/>
+    <col min="1" max="1" width="23.5" style="31" customWidth="1"/>
+    <col min="2" max="2" width="22.1719" style="31" customWidth="1"/>
+    <col min="3" max="5" width="14.5" style="31" customWidth="1"/>
+    <col min="6" max="16384" width="14.5" style="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="20">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="3"/>
@@ -10952,10 +10843,10 @@
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B2" t="s" s="25">
-        <v>48</v>
+        <v>370</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>46</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -10963,10 +10854,10 @@
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s" s="12">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -11037,62 +10928,62 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="31" customWidth="1"/>
-    <col min="2" max="2" width="11.8516" style="31" customWidth="1"/>
-    <col min="3" max="3" width="12" style="31" customWidth="1"/>
-    <col min="4" max="5" width="27.5" style="31" customWidth="1"/>
-    <col min="6" max="16384" width="14.5" style="31" customWidth="1"/>
+    <col min="1" max="1" width="23.5" style="32" customWidth="1"/>
+    <col min="2" max="2" width="11.8516" style="32" customWidth="1"/>
+    <col min="3" max="3" width="12" style="32" customWidth="1"/>
+    <col min="4" max="5" width="27.5" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="14.5" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
       <c r="A1" t="s" s="20">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s" s="21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s" s="21">
-        <v>14</v>
-      </c>
-      <c r="E1" t="s" s="27">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="E1" t="s" s="28">
+        <v>12</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s" s="25">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s" s="25">
-        <v>56</v>
-      </c>
-      <c r="E2" t="s" s="25">
-        <v>56</v>
+        <v>370</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s" s="26">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s" s="26">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s" s="26">
+        <v>54</v>
       </c>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="12">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B3" t="s" s="12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s" s="12">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D3" t="s" s="12">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E3" t="s" s="12">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" ht="13.55" customHeight="1">
@@ -11160,59 +11051,59 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="10.6719" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="14.5" style="32" customWidth="1"/>
+    <col min="1" max="5" width="10.6719" style="33" customWidth="1"/>
+    <col min="6" max="16384" width="14.5" style="33" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
-      <c r="A1" t="s" s="33">
-        <v>14</v>
+      <c r="A1" t="s" s="34">
+        <v>12</v>
       </c>
       <c r="B1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s" s="24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s" s="24">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s" s="29">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="E1" t="s" s="30">
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="B2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="C2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="D2" t="s" s="25">
-        <v>414</v>
-      </c>
-      <c r="E2" t="s" s="25">
-        <v>414</v>
+      <c r="A2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="B2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="C2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="D2" t="s" s="26">
+        <v>412</v>
+      </c>
+      <c r="E2" t="s" s="26">
+        <v>412</v>
       </c>
     </row>
     <row r="3" ht="13.55" customHeight="1">
       <c r="A3" t="s" s="12">
+        <v>413</v>
+      </c>
+      <c r="B3" t="s" s="12">
+        <v>414</v>
+      </c>
+      <c r="C3" t="s" s="12">
+        <v>315</v>
+      </c>
+      <c r="D3" t="s" s="12">
         <v>415</v>
       </c>
-      <c r="B3" t="s" s="12">
+      <c r="E3" t="s" s="12">
         <v>416</v>
-      </c>
-      <c r="C3" t="s" s="12">
-        <v>317</v>
-      </c>
-      <c r="D3" t="s" s="12">
-        <v>417</v>
-      </c>
-      <c r="E3" t="s" s="12">
-        <v>418</v>
       </c>
     </row>
     <row r="4" ht="13.55" customHeight="1">
